--- a/data/cost_forge.xlsx
+++ b/data/cost_forge.xlsx
@@ -533,7 +533,6 @@
           <t>UNIT</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
         <v>3</v>
       </c>
@@ -584,7 +583,6 @@
           <t>UNIT</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
         <v>2</v>
       </c>
@@ -635,7 +633,6 @@
           <t>UNIT</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
         <v>2</v>
       </c>
@@ -686,7 +683,6 @@
           <t>UNIT</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
         <v>2</v>
       </c>
@@ -737,7 +733,6 @@
           <t>UNIT</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
         <v>2</v>
       </c>
@@ -788,7 +783,6 @@
           <t>UNIT</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
         <v>1</v>
       </c>
@@ -839,7 +833,6 @@
           <t>UNIT</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
         <v>2</v>
       </c>
@@ -890,7 +883,6 @@
           <t>UNIT</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
         <v>1</v>
       </c>
@@ -941,7 +933,6 @@
           <t>UNIT</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
         <v>0</v>
       </c>
@@ -992,7 +983,6 @@
           <t>UNIT</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
         <v>0</v>
       </c>
@@ -1043,7 +1033,6 @@
           <t>UNIT</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="n">
         <v>0</v>
       </c>
@@ -1094,7 +1083,6 @@
           <t>UNIT</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
       <c r="M13" t="n">
         <v>0</v>
       </c>
@@ -1145,7 +1133,6 @@
           <t>UNIT</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr"/>
       <c r="M14" t="n">
         <v>3</v>
       </c>
@@ -1196,7 +1183,6 @@
           <t>UNIT</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr"/>
       <c r="M15" t="n">
         <v>2</v>
       </c>
@@ -1247,7 +1233,6 @@
           <t>UNIT</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr"/>
       <c r="M16" t="n">
         <v>2</v>
       </c>
@@ -1298,7 +1283,6 @@
           <t>UNIT</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr"/>
       <c r="M17" t="n">
         <v>2</v>
       </c>
@@ -1349,7 +1333,6 @@
           <t>UNIT</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr"/>
       <c r="M18" t="n">
         <v>2</v>
       </c>
@@ -1400,7 +1383,6 @@
           <t>UNIT</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr"/>
       <c r="M19" t="n">
         <v>1</v>
       </c>
@@ -1451,7 +1433,6 @@
           <t>UNIT</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr"/>
       <c r="M20" t="n">
         <v>0</v>
       </c>
@@ -1502,7 +1483,6 @@
           <t>UNIT</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr"/>
       <c r="M21" t="n">
         <v>2</v>
       </c>
@@ -1553,7 +1533,6 @@
           <t>UNIT</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr"/>
       <c r="M22" t="n">
         <v>0</v>
       </c>
@@ -1604,7 +1583,6 @@
           <t>UNIT</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr"/>
       <c r="M23" t="n">
         <v>0</v>
       </c>
@@ -1655,7 +1633,6 @@
           <t>UNIT</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr"/>
       <c r="M24" t="n">
         <v>3</v>
       </c>
@@ -1706,7 +1683,6 @@
           <t>UNIT</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr"/>
       <c r="M25" t="n">
         <v>3</v>
       </c>
@@ -1757,7 +1733,6 @@
           <t>UNIT</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr"/>
       <c r="M26" t="n">
         <v>2</v>
       </c>
@@ -1808,7 +1783,6 @@
           <t>UNIT</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr"/>
       <c r="M27" t="n">
         <v>0</v>
       </c>
@@ -1859,7 +1833,6 @@
           <t>UNIT</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr"/>
       <c r="M28" t="n">
         <v>2</v>
       </c>
@@ -1910,7 +1883,6 @@
           <t>UNIT</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr"/>
       <c r="M29" t="n">
         <v>2</v>
       </c>
@@ -1961,7 +1933,6 @@
           <t>UNIT</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr"/>
       <c r="M30" t="n">
         <v>2</v>
       </c>
@@ -2012,7 +1983,6 @@
           <t>UNIT</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr"/>
       <c r="M31" t="n">
         <v>2</v>
       </c>
@@ -2063,7 +2033,6 @@
           <t>UNIT</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr"/>
       <c r="M32" t="n">
         <v>1</v>
       </c>
@@ -2114,7 +2083,6 @@
           <t>UNIT</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr"/>
       <c r="M33" t="n">
         <v>1</v>
       </c>
@@ -2165,7 +2133,6 @@
           <t>UNIT</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr"/>
       <c r="M34" t="n">
         <v>0</v>
       </c>
@@ -2216,7 +2183,6 @@
           <t>UNIT</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr"/>
       <c r="M35" t="n">
         <v>0</v>
       </c>
@@ -2267,7 +2233,6 @@
           <t>UNIT</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr"/>
       <c r="M36" t="n">
         <v>0</v>
       </c>
@@ -2318,7 +2283,6 @@
           <t>UNIT</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr"/>
       <c r="M37" t="n">
         <v>2</v>
       </c>
@@ -2369,7 +2333,6 @@
           <t>UNIT</t>
         </is>
       </c>
-      <c r="L38" t="inlineStr"/>
       <c r="M38" t="n">
         <v>0</v>
       </c>
@@ -2420,7 +2383,6 @@
           <t>UNIT</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr"/>
       <c r="M39" t="n">
         <v>2</v>
       </c>
@@ -2471,7 +2433,6 @@
           <t>UNIT</t>
         </is>
       </c>
-      <c r="L40" t="inlineStr"/>
       <c r="M40" t="n">
         <v>2</v>
       </c>
@@ -2522,7 +2483,6 @@
           <t>UNIT</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr"/>
       <c r="M41" t="n">
         <v>2</v>
       </c>
@@ -2573,7 +2533,6 @@
           <t>UNIT</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr"/>
       <c r="M42" t="n">
         <v>2</v>
       </c>
@@ -2624,7 +2583,6 @@
           <t>UNIT</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr"/>
       <c r="M43" t="n">
         <v>2</v>
       </c>
@@ -2675,7 +2633,6 @@
           <t>UNIT</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr"/>
       <c r="M44" t="n">
         <v>2</v>
       </c>
@@ -2726,7 +2683,6 @@
           <t>UNIT</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr"/>
       <c r="M45" t="n">
         <v>1</v>
       </c>
@@ -2777,7 +2733,6 @@
           <t>UNIT</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr"/>
       <c r="M46" t="n">
         <v>0</v>
       </c>
@@ -2828,7 +2783,6 @@
           <t>UNIT</t>
         </is>
       </c>
-      <c r="L47" t="inlineStr"/>
       <c r="M47" t="n">
         <v>1</v>
       </c>
@@ -2879,7 +2833,6 @@
           <t>UNIT</t>
         </is>
       </c>
-      <c r="L48" t="inlineStr"/>
       <c r="M48" t="n">
         <v>0</v>
       </c>
@@ -2930,7 +2883,6 @@
           <t>UNIT</t>
         </is>
       </c>
-      <c r="L49" t="inlineStr"/>
       <c r="M49" t="n">
         <v>0</v>
       </c>
@@ -2981,7 +2933,6 @@
           <t>UNIT</t>
         </is>
       </c>
-      <c r="L50" t="inlineStr"/>
       <c r="M50" t="n">
         <v>0</v>
       </c>
@@ -3032,7 +2983,6 @@
           <t>UNIT</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr"/>
       <c r="M51" t="n">
         <v>2</v>
       </c>
@@ -3083,7 +3033,6 @@
           <t>UNIT</t>
         </is>
       </c>
-      <c r="L52" t="inlineStr"/>
       <c r="M52" t="n">
         <v>2</v>
       </c>
@@ -3134,7 +3083,6 @@
           <t>UNIT</t>
         </is>
       </c>
-      <c r="L53" t="inlineStr"/>
       <c r="M53" t="n">
         <v>2</v>
       </c>
@@ -3185,7 +3133,6 @@
           <t>UNIT</t>
         </is>
       </c>
-      <c r="L54" t="inlineStr"/>
       <c r="M54" t="n">
         <v>0</v>
       </c>
@@ -3236,7 +3183,6 @@
           <t>UNIT</t>
         </is>
       </c>
-      <c r="L55" t="inlineStr"/>
       <c r="M55" t="n">
         <v>1</v>
       </c>
@@ -3287,7 +3233,6 @@
           <t>UNIT</t>
         </is>
       </c>
-      <c r="L56" t="inlineStr"/>
       <c r="M56" t="n">
         <v>2</v>
       </c>
@@ -3338,7 +3283,6 @@
           <t>UNIT</t>
         </is>
       </c>
-      <c r="L57" t="inlineStr"/>
       <c r="M57" t="n">
         <v>1</v>
       </c>
@@ -3389,7 +3333,6 @@
           <t>UNIT</t>
         </is>
       </c>
-      <c r="L58" t="inlineStr"/>
       <c r="M58" t="n">
         <v>0</v>
       </c>
@@ -3440,7 +3383,6 @@
           <t>UNIT</t>
         </is>
       </c>
-      <c r="L59" t="inlineStr"/>
       <c r="M59" t="n">
         <v>0</v>
       </c>
@@ -3491,7 +3433,6 @@
           <t>UNIT</t>
         </is>
       </c>
-      <c r="L60" t="inlineStr"/>
       <c r="M60" t="n">
         <v>0</v>
       </c>
@@ -3542,7 +3483,6 @@
           <t>UNIT</t>
         </is>
       </c>
-      <c r="L61" t="inlineStr"/>
       <c r="M61" t="n">
         <v>2</v>
       </c>
@@ -3593,7 +3533,6 @@
           <t>UNIT</t>
         </is>
       </c>
-      <c r="L62" t="inlineStr"/>
       <c r="M62" t="n">
         <v>2</v>
       </c>
@@ -3644,7 +3583,6 @@
           <t>UNIT</t>
         </is>
       </c>
-      <c r="L63" t="inlineStr"/>
       <c r="M63" t="n">
         <v>2</v>
       </c>
@@ -3695,7 +3633,6 @@
           <t>UNIT</t>
         </is>
       </c>
-      <c r="L64" t="inlineStr"/>
       <c r="M64" t="n">
         <v>2</v>
       </c>
@@ -3746,7 +3683,6 @@
           <t>UNIT</t>
         </is>
       </c>
-      <c r="L65" t="inlineStr"/>
       <c r="M65" t="n">
         <v>2</v>
       </c>
@@ -3797,7 +3733,6 @@
           <t>UNIT</t>
         </is>
       </c>
-      <c r="L66" t="inlineStr"/>
       <c r="M66" t="n">
         <v>2</v>
       </c>
@@ -3848,7 +3783,6 @@
           <t>UNIT</t>
         </is>
       </c>
-      <c r="L67" t="inlineStr"/>
       <c r="M67" t="n">
         <v>2</v>
       </c>
@@ -3899,7 +3833,6 @@
           <t>UNIT</t>
         </is>
       </c>
-      <c r="L68" t="inlineStr"/>
       <c r="M68" t="n">
         <v>1</v>
       </c>
@@ -3950,7 +3883,6 @@
           <t>UNIT</t>
         </is>
       </c>
-      <c r="L69" t="inlineStr"/>
       <c r="M69" t="n">
         <v>0</v>
       </c>
@@ -4001,7 +3933,6 @@
           <t>UNIT</t>
         </is>
       </c>
-      <c r="L70" t="inlineStr"/>
       <c r="M70" t="n">
         <v>0</v>
       </c>
@@ -4052,7 +3983,6 @@
           <t>UNIT</t>
         </is>
       </c>
-      <c r="L71" t="inlineStr"/>
       <c r="M71" t="n">
         <v>0</v>
       </c>
@@ -4103,7 +4033,6 @@
           <t>UNIT</t>
         </is>
       </c>
-      <c r="L72" t="inlineStr"/>
       <c r="M72" t="n">
         <v>2</v>
       </c>
@@ -4154,7 +4083,6 @@
           <t>UNIT</t>
         </is>
       </c>
-      <c r="L73" t="inlineStr"/>
       <c r="M73" t="n">
         <v>2</v>
       </c>
@@ -4205,7 +4133,6 @@
           <t>UNIT</t>
         </is>
       </c>
-      <c r="L74" t="inlineStr"/>
       <c r="M74" t="n">
         <v>2</v>
       </c>
@@ -4256,7 +4183,6 @@
           <t>UNIT</t>
         </is>
       </c>
-      <c r="L75" t="inlineStr"/>
       <c r="M75" t="n">
         <v>2</v>
       </c>
@@ -4307,7 +4233,6 @@
           <t>UNIT</t>
         </is>
       </c>
-      <c r="L76" t="inlineStr"/>
       <c r="M76" t="n">
         <v>1</v>
       </c>
@@ -4358,7 +4283,6 @@
           <t>UNIT</t>
         </is>
       </c>
-      <c r="L77" t="inlineStr"/>
       <c r="M77" t="n">
         <v>1</v>
       </c>
@@ -4409,7 +4333,6 @@
           <t>UNIT</t>
         </is>
       </c>
-      <c r="L78" t="inlineStr"/>
       <c r="M78" t="n">
         <v>0</v>
       </c>
@@ -4460,7 +4383,6 @@
           <t>UNIT</t>
         </is>
       </c>
-      <c r="L79" t="inlineStr"/>
       <c r="M79" t="n">
         <v>0</v>
       </c>
@@ -4511,7 +4433,6 @@
           <t>UNIT</t>
         </is>
       </c>
-      <c r="L80" t="inlineStr"/>
       <c r="M80" t="n">
         <v>0</v>
       </c>
@@ -4562,7 +4483,6 @@
           <t>UNIT</t>
         </is>
       </c>
-      <c r="L81" t="inlineStr"/>
       <c r="M81" t="n">
         <v>2</v>
       </c>
@@ -4613,7 +4533,6 @@
           <t>UNIT</t>
         </is>
       </c>
-      <c r="L82" t="inlineStr"/>
       <c r="M82" t="n">
         <v>2</v>
       </c>
@@ -4664,7 +4583,6 @@
           <t>UNIT</t>
         </is>
       </c>
-      <c r="L83" t="inlineStr"/>
       <c r="M83" t="n">
         <v>2</v>
       </c>
@@ -4715,7 +4633,6 @@
           <t>UNIT</t>
         </is>
       </c>
-      <c r="L84" t="inlineStr"/>
       <c r="M84" t="n">
         <v>2</v>
       </c>
@@ -4766,7 +4683,6 @@
           <t>UNIT</t>
         </is>
       </c>
-      <c r="L85" t="inlineStr"/>
       <c r="M85" t="n">
         <v>2</v>
       </c>
@@ -4817,7 +4733,6 @@
           <t>UNIT</t>
         </is>
       </c>
-      <c r="L86" t="inlineStr"/>
       <c r="M86" t="n">
         <v>2</v>
       </c>
@@ -4868,7 +4783,6 @@
           <t>UNIT</t>
         </is>
       </c>
-      <c r="L87" t="inlineStr"/>
       <c r="M87" t="n">
         <v>1</v>
       </c>
@@ -4919,7 +4833,6 @@
           <t>UNIT</t>
         </is>
       </c>
-      <c r="L88" t="inlineStr"/>
       <c r="M88" t="n">
         <v>1</v>
       </c>
@@ -4970,7 +4883,6 @@
           <t>UNIT</t>
         </is>
       </c>
-      <c r="L89" t="inlineStr"/>
       <c r="M89" t="n">
         <v>1</v>
       </c>
@@ -5021,7 +4933,6 @@
           <t>UNIT</t>
         </is>
       </c>
-      <c r="L90" t="inlineStr"/>
       <c r="M90" t="n">
         <v>0</v>
       </c>
@@ -5072,7 +4983,6 @@
           <t>UNIT</t>
         </is>
       </c>
-      <c r="L91" t="inlineStr"/>
       <c r="M91" t="n">
         <v>2</v>
       </c>
@@ -5123,7 +5033,6 @@
           <t>UNIT</t>
         </is>
       </c>
-      <c r="L92" t="inlineStr"/>
       <c r="M92" t="n">
         <v>2</v>
       </c>
@@ -5174,7 +5083,6 @@
           <t>UNIT</t>
         </is>
       </c>
-      <c r="L93" t="inlineStr"/>
       <c r="M93" t="n">
         <v>1</v>
       </c>
@@ -5225,7 +5133,6 @@
           <t>UNIT</t>
         </is>
       </c>
-      <c r="L94" t="inlineStr"/>
       <c r="M94" t="n">
         <v>2</v>
       </c>
@@ -5276,7 +5183,6 @@
           <t>UNIT</t>
         </is>
       </c>
-      <c r="L95" t="inlineStr"/>
       <c r="M95" t="n">
         <v>2</v>
       </c>
@@ -5327,7 +5233,6 @@
           <t>UNIT</t>
         </is>
       </c>
-      <c r="L96" t="inlineStr"/>
       <c r="M96" t="n">
         <v>1</v>
       </c>
@@ -5378,7 +5283,6 @@
           <t>UNIT</t>
         </is>
       </c>
-      <c r="L97" t="inlineStr"/>
       <c r="M97" t="n">
         <v>1</v>
       </c>
@@ -5429,7 +5333,6 @@
           <t>UNIT</t>
         </is>
       </c>
-      <c r="L98" t="inlineStr"/>
       <c r="M98" t="n">
         <v>1</v>
       </c>
@@ -5480,7 +5383,6 @@
           <t>UNIT</t>
         </is>
       </c>
-      <c r="L99" t="inlineStr"/>
       <c r="M99" t="n">
         <v>0</v>
       </c>
@@ -5531,7 +5433,6 @@
           <t>UNIT</t>
         </is>
       </c>
-      <c r="L100" t="inlineStr"/>
       <c r="M100" t="n">
         <v>0</v>
       </c>
@@ -5582,7 +5483,6 @@
           <t>UNIT</t>
         </is>
       </c>
-      <c r="L101" t="inlineStr"/>
       <c r="M101" t="n">
         <v>2</v>
       </c>
@@ -5633,7 +5533,6 @@
           <t>UNIT</t>
         </is>
       </c>
-      <c r="L102" t="inlineStr"/>
       <c r="M102" t="n">
         <v>2</v>
       </c>
@@ -5684,7 +5583,6 @@
           <t>UNIT</t>
         </is>
       </c>
-      <c r="L103" t="inlineStr"/>
       <c r="M103" t="n">
         <v>2</v>
       </c>
@@ -5735,7 +5633,6 @@
           <t>UNIT</t>
         </is>
       </c>
-      <c r="L104" t="inlineStr"/>
       <c r="M104" t="n">
         <v>2</v>
       </c>
@@ -5786,7 +5683,6 @@
           <t>UNIT</t>
         </is>
       </c>
-      <c r="L105" t="inlineStr"/>
       <c r="M105" t="n">
         <v>2</v>
       </c>
@@ -5837,7 +5733,6 @@
           <t>UNIT</t>
         </is>
       </c>
-      <c r="L106" t="inlineStr"/>
       <c r="M106" t="n">
         <v>2</v>
       </c>
@@ -5888,7 +5783,6 @@
           <t>UNIT</t>
         </is>
       </c>
-      <c r="L107" t="inlineStr"/>
       <c r="M107" t="n">
         <v>0</v>
       </c>
@@ -5939,7 +5833,6 @@
           <t>UNIT</t>
         </is>
       </c>
-      <c r="L108" t="inlineStr"/>
       <c r="M108" t="n">
         <v>2</v>
       </c>
@@ -5990,7 +5883,6 @@
           <t>UNIT</t>
         </is>
       </c>
-      <c r="L109" t="inlineStr"/>
       <c r="M109" t="n">
         <v>0</v>
       </c>
@@ -6041,7 +5933,6 @@
           <t>UNIT</t>
         </is>
       </c>
-      <c r="L110" t="inlineStr"/>
       <c r="M110" t="n">
         <v>2</v>
       </c>
@@ -6092,7 +5983,6 @@
           <t>UNIT</t>
         </is>
       </c>
-      <c r="L111" t="inlineStr"/>
       <c r="M111" t="n">
         <v>2</v>
       </c>
@@ -6143,7 +6033,6 @@
           <t>UNIT</t>
         </is>
       </c>
-      <c r="L112" t="inlineStr"/>
       <c r="M112" t="n">
         <v>0</v>
       </c>
@@ -6194,7 +6083,6 @@
           <t>UNIT</t>
         </is>
       </c>
-      <c r="L113" t="inlineStr"/>
       <c r="M113" t="n">
         <v>1</v>
       </c>
@@ -6245,7 +6133,6 @@
           <t>UNIT</t>
         </is>
       </c>
-      <c r="L114" t="inlineStr"/>
       <c r="M114" t="n">
         <v>1</v>
       </c>
@@ -6296,7 +6183,6 @@
           <t>UNIT</t>
         </is>
       </c>
-      <c r="L115" t="inlineStr"/>
       <c r="M115" t="n">
         <v>1</v>
       </c>
@@ -6347,7 +6233,6 @@
           <t>UNIT</t>
         </is>
       </c>
-      <c r="L116" t="inlineStr"/>
       <c r="M116" t="n">
         <v>1</v>
       </c>
@@ -6398,7 +6283,6 @@
           <t>UNIT</t>
         </is>
       </c>
-      <c r="L117" t="inlineStr"/>
       <c r="M117" t="n">
         <v>2</v>
       </c>
@@ -6449,7 +6333,6 @@
           <t>UNIT</t>
         </is>
       </c>
-      <c r="L118" t="inlineStr"/>
       <c r="M118" t="n">
         <v>0</v>
       </c>
@@ -6500,7 +6383,6 @@
           <t>UNIT</t>
         </is>
       </c>
-      <c r="L119" t="inlineStr"/>
       <c r="M119" t="n">
         <v>0</v>
       </c>
@@ -6551,7 +6433,6 @@
           <t>UNIT</t>
         </is>
       </c>
-      <c r="L120" t="inlineStr"/>
       <c r="M120" t="n">
         <v>1</v>
       </c>
@@ -6602,7 +6483,6 @@
           <t>UNIT</t>
         </is>
       </c>
-      <c r="L121" t="inlineStr"/>
       <c r="M121" t="n">
         <v>1</v>
       </c>
@@ -6653,7 +6533,6 @@
           <t>UNIT</t>
         </is>
       </c>
-      <c r="L122" t="inlineStr"/>
       <c r="M122" t="n">
         <v>1</v>
       </c>
@@ -6704,7 +6583,6 @@
           <t>UNIT</t>
         </is>
       </c>
-      <c r="L123" t="inlineStr"/>
       <c r="M123" t="n">
         <v>1</v>
       </c>
@@ -6755,7 +6633,6 @@
           <t>UNIT</t>
         </is>
       </c>
-      <c r="L124" t="inlineStr"/>
       <c r="M124" t="n">
         <v>1</v>
       </c>
@@ -6806,7 +6683,6 @@
           <t>UNIT</t>
         </is>
       </c>
-      <c r="L125" t="inlineStr"/>
       <c r="M125" t="n">
         <v>1</v>
       </c>
@@ -6857,7 +6733,6 @@
           <t>UNIT</t>
         </is>
       </c>
-      <c r="L126" t="inlineStr"/>
       <c r="M126" t="n">
         <v>1</v>
       </c>
@@ -6908,7 +6783,6 @@
           <t>UNIT</t>
         </is>
       </c>
-      <c r="L127" t="inlineStr"/>
       <c r="M127" t="n">
         <v>0</v>
       </c>
@@ -6959,7 +6833,6 @@
           <t>UNIT</t>
         </is>
       </c>
-      <c r="L128" t="inlineStr"/>
       <c r="M128" t="n">
         <v>0</v>
       </c>
@@ -7010,7 +6883,6 @@
           <t>UNIT</t>
         </is>
       </c>
-      <c r="L129" t="inlineStr"/>
       <c r="M129" t="n">
         <v>0</v>
       </c>
@@ -7061,7 +6933,6 @@
           <t>UNIT</t>
         </is>
       </c>
-      <c r="L130" t="inlineStr"/>
       <c r="M130" t="n">
         <v>0</v>
       </c>
@@ -7112,7 +6983,6 @@
           <t>UNIT</t>
         </is>
       </c>
-      <c r="L131" t="inlineStr"/>
       <c r="M131" t="n">
         <v>0</v>
       </c>
@@ -7163,7 +7033,6 @@
           <t>UNIT</t>
         </is>
       </c>
-      <c r="L132" t="inlineStr"/>
       <c r="M132" t="n">
         <v>0</v>
       </c>
@@ -7214,7 +7083,6 @@
           <t>UNIT</t>
         </is>
       </c>
-      <c r="L133" t="inlineStr"/>
       <c r="M133" t="n">
         <v>0</v>
       </c>
@@ -7265,7 +7133,6 @@
           <t>UNIT</t>
         </is>
       </c>
-      <c r="L134" t="inlineStr"/>
       <c r="M134" t="n">
         <v>0</v>
       </c>
@@ -7316,7 +7183,6 @@
           <t>UNIT</t>
         </is>
       </c>
-      <c r="L135" t="inlineStr"/>
       <c r="M135" t="n">
         <v>0</v>
       </c>
@@ -7367,7 +7233,6 @@
           <t>UNIT</t>
         </is>
       </c>
-      <c r="L136" t="inlineStr"/>
       <c r="M136" t="n">
         <v>0</v>
       </c>
@@ -7418,7 +7283,6 @@
           <t>UNIT</t>
         </is>
       </c>
-      <c r="L137" t="inlineStr"/>
       <c r="M137" t="n">
         <v>0</v>
       </c>
@@ -7469,7 +7333,6 @@
           <t>UNIT</t>
         </is>
       </c>
-      <c r="L138" t="inlineStr"/>
       <c r="M138" t="n">
         <v>0</v>
       </c>
@@ -7520,7 +7383,6 @@
           <t>UNIT</t>
         </is>
       </c>
-      <c r="L139" t="inlineStr"/>
       <c r="M139" t="n">
         <v>0</v>
       </c>
@@ -7571,7 +7433,6 @@
           <t>UNIT</t>
         </is>
       </c>
-      <c r="L140" t="inlineStr"/>
       <c r="M140" t="n">
         <v>0</v>
       </c>
@@ -7622,7 +7483,6 @@
           <t>UNIT</t>
         </is>
       </c>
-      <c r="L141" t="inlineStr"/>
       <c r="M141" t="n">
         <v>0</v>
       </c>
@@ -7673,7 +7533,6 @@
           <t>UNIT</t>
         </is>
       </c>
-      <c r="L142" t="inlineStr"/>
       <c r="M142" t="n">
         <v>0</v>
       </c>
@@ -7724,7 +7583,6 @@
           <t>UNIT</t>
         </is>
       </c>
-      <c r="L143" t="inlineStr"/>
       <c r="M143" t="n">
         <v>0</v>
       </c>
@@ -7775,7 +7633,6 @@
           <t>UNIT</t>
         </is>
       </c>
-      <c r="L144" t="inlineStr"/>
       <c r="M144" t="n">
         <v>0</v>
       </c>
@@ -8147,7 +8004,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8587,6 +8444,726 @@
         <v>0.2</v>
       </c>
       <c r="F18" t="n">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>CNC_LATHE_GEN</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>CNC turning — general purpose</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>65</v>
+      </c>
+      <c r="D19" t="n">
+        <v>45</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>CNC_MILL_4AX</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>4-axis CNC milling</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>120</v>
+      </c>
+      <c r="D20" t="n">
+        <v>60</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>TURN_MILL</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Turn-mill combined (multi-tasking centre)</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>145</v>
+      </c>
+      <c r="D21" t="n">
+        <v>65</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>DEEP_HOLE_DRILL</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Deep hole / gun drilling</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>95</v>
+      </c>
+      <c r="D22" t="n">
+        <v>45</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>HONING</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Internal honing (cylinders / bores)</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>75</v>
+      </c>
+      <c r="D23" t="n">
+        <v>45</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>LAPPING</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Precision lapping (sealing faces)</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>65</v>
+      </c>
+      <c r="D24" t="n">
+        <v>50</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>JIG_BORE</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Jig boring — precision hole patterns</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>100</v>
+      </c>
+      <c r="D25" t="n">
+        <v>55</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>THREAD_GRIND</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Thread grinding (precision screws / nuts)</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>85</v>
+      </c>
+      <c r="D26" t="n">
+        <v>50</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>GEAR_CUT</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Gear cutting / hobbing</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>110</v>
+      </c>
+      <c r="D27" t="n">
+        <v>55</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>MIG_WELD</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>MIG / MAG welding — structural</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>50</v>
+      </c>
+      <c r="D28" t="n">
+        <v>55</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>PIPE_WELD</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Pipe &amp; tube welding — certified</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>65</v>
+      </c>
+      <c r="D29" t="n">
+        <v>70</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>WELD_OVERLAY</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Weld overlay / hard-facing cladding</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>70</v>
+      </c>
+      <c r="D30" t="n">
+        <v>65</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>LASER_WELD</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Laser welding — thin section precision</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>120</v>
+      </c>
+      <c r="D31" t="n">
+        <v>55</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>LASER_CUT</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Laser cutting — sheet and plate</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>85</v>
+      </c>
+      <c r="D32" t="n">
+        <v>35</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>FLAME_CUT</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Oxy-fuel cutting — heavy plate</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>55</v>
+      </c>
+      <c r="D33" t="n">
+        <v>35</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>PRESS_BRAKE</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Press brake forming — sheet / plate</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>60</v>
+      </c>
+      <c r="D34" t="n">
+        <v>40</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>ROLL_FORM</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Plate / section rolling (cylinders, rings)</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>55</v>
+      </c>
+      <c r="D35" t="n">
+        <v>40</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>INVEST_CAST</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Investment casting (lost-wax)</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>55</v>
+      </c>
+      <c r="D36" t="n">
+        <v>45</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>CENTRIFUGAL</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Centrifugal casting (tubes / rings)</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>50</v>
+      </c>
+      <c r="D37" t="n">
+        <v>40</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>FORGING</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Drop forging — hot / warm</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>95</v>
+      </c>
+      <c r="D38" t="n">
+        <v>45</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>HEAT_TREAT</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Heat treatment (stress relief / anneal / quench)</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>40</v>
+      </c>
+      <c r="D39" t="n">
+        <v>30</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>SHOT_PEEN</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Shot peening (fatigue improvement)</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>45</v>
+      </c>
+      <c r="D40" t="n">
+        <v>35</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>HOT_DIP_GALV</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Hot-dip galvanising</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>40</v>
+      </c>
+      <c r="D41" t="n">
+        <v>30</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>NITRIDING</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Gas / plasma nitriding</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>60</v>
+      </c>
+      <c r="D42" t="n">
+        <v>40</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>RUBBER_BOND</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Rubber bonding / vulcanising</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>45</v>
+      </c>
+      <c r="D43" t="n">
+        <v>40</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>CMM_INSPECT</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>CMM dimensional inspection</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>75</v>
+      </c>
+      <c r="D44" t="n">
+        <v>65</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>RADIOGRAPHY</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>X-ray radiography NDT</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>90</v>
+      </c>
+      <c r="D45" t="n">
+        <v>75</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>FLOW_TEST</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Flow / performance acceptance test</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>60</v>
+      </c>
+      <c r="D46" t="n">
+        <v>55</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>LEAK_TEST</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Helium / pneumatic leak test</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>55</v>
+      </c>
+      <c r="D47" t="n">
+        <v>50</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="F47" t="n">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>VIBRATION_TEST</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Vibration / fatigue testing</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>70</v>
+      </c>
+      <c r="D48" t="n">
+        <v>60</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="F48" t="n">
         <v>0.15</v>
       </c>
     </row>
@@ -9104,10 +9681,6 @@
           <t>I01</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
           <t>not_started</t>
@@ -9120,10 +9693,6 @@
           <t>I02</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
           <t>not_started</t>
@@ -9136,10 +9705,6 @@
           <t>I03</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
           <t>not_started</t>
@@ -9152,10 +9717,6 @@
           <t>I04</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
           <t>not_started</t>
@@ -9168,10 +9729,6 @@
           <t>I05</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
           <t>not_started</t>
@@ -9184,10 +9741,6 @@
           <t>I06</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
           <t>not_started</t>
@@ -9200,10 +9753,6 @@
           <t>I07</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
           <t>not_started</t>
@@ -9216,10 +9765,6 @@
           <t>I08</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
           <t>not_started</t>
@@ -9232,10 +9777,6 @@
           <t>I09</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
           <t>not_started</t>
@@ -9248,10 +9789,6 @@
           <t>I10</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
           <t>not_started</t>
@@ -9264,10 +9801,6 @@
           <t>I11</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
           <t>not_started</t>
@@ -9280,10 +9813,6 @@
           <t>I12</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
           <t>not_started</t>
@@ -9296,10 +9825,6 @@
           <t>SB01</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
           <t>not_started</t>
@@ -9312,10 +9837,6 @@
           <t>SB02</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
           <t>not_started</t>
@@ -9328,10 +9849,6 @@
           <t>SB03</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
           <t>not_started</t>
@@ -9344,10 +9861,6 @@
           <t>SB04</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
           <t>not_started</t>
@@ -9360,10 +9873,6 @@
           <t>SB05</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
           <t>not_started</t>
@@ -9376,10 +9885,6 @@
           <t>SB06</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
           <t>not_started</t>
@@ -9392,10 +9897,6 @@
           <t>SB07</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
           <t>not_started</t>
@@ -9408,10 +9909,6 @@
           <t>SB08</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
           <t>not_started</t>
@@ -9424,10 +9921,6 @@
           <t>SB09</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr"/>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
           <t>not_started</t>
@@ -9440,10 +9933,6 @@
           <t>SB10</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr"/>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
           <t>not_started</t>
@@ -9456,10 +9945,6 @@
           <t>H01</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr"/>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
           <t>not_started</t>
@@ -9472,10 +9957,6 @@
           <t>H02</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr"/>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
           <t>not_started</t>
@@ -9488,10 +9969,6 @@
           <t>H03</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr"/>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
           <t>not_started</t>
@@ -9504,10 +9981,6 @@
           <t>H04</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr"/>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
           <t>not_started</t>
@@ -9520,10 +9993,6 @@
           <t>H05</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr"/>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
           <t>not_started</t>
@@ -9536,10 +10005,6 @@
           <t>H06</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr"/>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
           <t>not_started</t>
@@ -9552,10 +10017,6 @@
           <t>H07</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr"/>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
           <t>not_started</t>
@@ -9568,10 +10029,6 @@
           <t>H08</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr"/>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
           <t>not_started</t>
@@ -9584,10 +10041,6 @@
           <t>H09</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr"/>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
           <t>not_started</t>
@@ -9600,10 +10053,6 @@
           <t>H10</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr"/>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
           <t>not_started</t>
@@ -9616,10 +10065,6 @@
           <t>H11</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr"/>
-      <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
           <t>not_started</t>
@@ -9632,10 +10077,6 @@
           <t>H12</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr"/>
-      <c r="C35" t="inlineStr"/>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
           <t>not_started</t>
@@ -9648,10 +10089,6 @@
           <t>H13</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr"/>
-      <c r="C36" t="inlineStr"/>
-      <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
           <t>not_started</t>
@@ -9664,10 +10101,6 @@
           <t>S01</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr"/>
-      <c r="C37" t="inlineStr"/>
-      <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
           <t>not_started</t>
@@ -9680,10 +10113,6 @@
           <t>S02</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr"/>
-      <c r="C38" t="inlineStr"/>
-      <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
           <t>not_started</t>
@@ -9696,10 +10125,6 @@
           <t>S03</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr"/>
-      <c r="C39" t="inlineStr"/>
-      <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
           <t>not_started</t>
@@ -9712,10 +10137,6 @@
           <t>S04</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr"/>
-      <c r="C40" t="inlineStr"/>
-      <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
           <t>not_started</t>
@@ -9728,10 +10149,6 @@
           <t>S05</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr"/>
-      <c r="C41" t="inlineStr"/>
-      <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
           <t>not_started</t>
@@ -9744,10 +10161,6 @@
           <t>S06</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr"/>
-      <c r="C42" t="inlineStr"/>
-      <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
           <t>not_started</t>
@@ -9760,10 +10173,6 @@
           <t>S07</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr"/>
-      <c r="C43" t="inlineStr"/>
-      <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
           <t>not_started</t>
@@ -9776,10 +10185,6 @@
           <t>S08</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr"/>
-      <c r="C44" t="inlineStr"/>
-      <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
           <t>not_started</t>
@@ -9792,10 +10197,6 @@
           <t>S09</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr"/>
-      <c r="C45" t="inlineStr"/>
-      <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
           <t>not_started</t>
@@ -9808,10 +10209,6 @@
           <t>S10</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr"/>
-      <c r="C46" t="inlineStr"/>
-      <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
           <t>not_started</t>
@@ -9824,10 +10221,6 @@
           <t>S11</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr"/>
-      <c r="C47" t="inlineStr"/>
-      <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
           <t>not_started</t>
@@ -9840,10 +10233,6 @@
           <t>S12</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr"/>
-      <c r="C48" t="inlineStr"/>
-      <c r="D48" t="inlineStr"/>
-      <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
           <t>not_started</t>
@@ -9856,10 +10245,6 @@
           <t>S13</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr"/>
-      <c r="C49" t="inlineStr"/>
-      <c r="D49" t="inlineStr"/>
-      <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
           <t>not_started</t>
@@ -9872,10 +10257,6 @@
           <t>S14</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr"/>
-      <c r="C50" t="inlineStr"/>
-      <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
           <t>not_started</t>
@@ -9888,10 +10269,6 @@
           <t>TB01</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr"/>
-      <c r="C51" t="inlineStr"/>
-      <c r="D51" t="inlineStr"/>
-      <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
           <t>not_started</t>
@@ -9904,10 +10281,6 @@
           <t>TB02</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr"/>
-      <c r="C52" t="inlineStr"/>
-      <c r="D52" t="inlineStr"/>
-      <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
           <t>not_started</t>
@@ -9920,10 +10293,6 @@
           <t>TB03</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr"/>
-      <c r="C53" t="inlineStr"/>
-      <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
           <t>not_started</t>
@@ -9936,10 +10305,6 @@
           <t>TB04</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr"/>
-      <c r="C54" t="inlineStr"/>
-      <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
           <t>not_started</t>
@@ -9952,10 +10317,6 @@
           <t>TB05</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr"/>
-      <c r="C55" t="inlineStr"/>
-      <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
           <t>not_started</t>
@@ -9968,10 +10329,6 @@
           <t>TB06</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr"/>
-      <c r="C56" t="inlineStr"/>
-      <c r="D56" t="inlineStr"/>
-      <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
           <t>not_started</t>
@@ -9984,10 +10341,6 @@
           <t>TB07</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr"/>
-      <c r="C57" t="inlineStr"/>
-      <c r="D57" t="inlineStr"/>
-      <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
           <t>not_started</t>
@@ -10000,10 +10353,6 @@
           <t>TB08</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr"/>
-      <c r="C58" t="inlineStr"/>
-      <c r="D58" t="inlineStr"/>
-      <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
           <t>not_started</t>
@@ -10016,10 +10365,6 @@
           <t>TB09</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr"/>
-      <c r="C59" t="inlineStr"/>
-      <c r="D59" t="inlineStr"/>
-      <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
           <t>not_started</t>
@@ -10032,10 +10377,6 @@
           <t>TB10</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr"/>
-      <c r="C60" t="inlineStr"/>
-      <c r="D60" t="inlineStr"/>
-      <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
           <t>not_started</t>
@@ -10048,10 +10389,6 @@
           <t>D01</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr"/>
-      <c r="C61" t="inlineStr"/>
-      <c r="D61" t="inlineStr"/>
-      <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
           <t>not_started</t>
@@ -10064,10 +10401,6 @@
           <t>D02</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr"/>
-      <c r="C62" t="inlineStr"/>
-      <c r="D62" t="inlineStr"/>
-      <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
         <is>
           <t>not_started</t>
@@ -10080,10 +10413,6 @@
           <t>D03</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr"/>
-      <c r="C63" t="inlineStr"/>
-      <c r="D63" t="inlineStr"/>
-      <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
           <t>not_started</t>
@@ -10096,10 +10425,6 @@
           <t>D04</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr"/>
-      <c r="C64" t="inlineStr"/>
-      <c r="D64" t="inlineStr"/>
-      <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr">
         <is>
           <t>not_started</t>
@@ -10112,10 +10437,6 @@
           <t>D05</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr"/>
-      <c r="C65" t="inlineStr"/>
-      <c r="D65" t="inlineStr"/>
-      <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr">
         <is>
           <t>not_started</t>
@@ -10128,10 +10449,6 @@
           <t>D06</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr"/>
-      <c r="C66" t="inlineStr"/>
-      <c r="D66" t="inlineStr"/>
-      <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
           <t>not_started</t>
@@ -10144,10 +10461,6 @@
           <t>D07</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr"/>
-      <c r="C67" t="inlineStr"/>
-      <c r="D67" t="inlineStr"/>
-      <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
           <t>not_started</t>
@@ -10160,10 +10473,6 @@
           <t>D08</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr"/>
-      <c r="C68" t="inlineStr"/>
-      <c r="D68" t="inlineStr"/>
-      <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
         <is>
           <t>not_started</t>
@@ -10176,10 +10485,6 @@
           <t>D09</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr"/>
-      <c r="C69" t="inlineStr"/>
-      <c r="D69" t="inlineStr"/>
-      <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr">
         <is>
           <t>not_started</t>
@@ -10192,10 +10497,6 @@
           <t>D10</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr"/>
-      <c r="C70" t="inlineStr"/>
-      <c r="D70" t="inlineStr"/>
-      <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr">
         <is>
           <t>not_started</t>
@@ -10208,10 +10509,6 @@
           <t>D11</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr"/>
-      <c r="C71" t="inlineStr"/>
-      <c r="D71" t="inlineStr"/>
-      <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
           <t>not_started</t>
@@ -10224,10 +10521,6 @@
           <t>N01</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr"/>
-      <c r="C72" t="inlineStr"/>
-      <c r="D72" t="inlineStr"/>
-      <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr">
         <is>
           <t>not_started</t>
@@ -10240,10 +10533,6 @@
           <t>N02</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr"/>
-      <c r="C73" t="inlineStr"/>
-      <c r="D73" t="inlineStr"/>
-      <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr">
         <is>
           <t>not_started</t>
@@ -10256,10 +10545,6 @@
           <t>N03</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr"/>
-      <c r="C74" t="inlineStr"/>
-      <c r="D74" t="inlineStr"/>
-      <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr">
         <is>
           <t>not_started</t>
@@ -10272,10 +10557,6 @@
           <t>N04</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr"/>
-      <c r="C75" t="inlineStr"/>
-      <c r="D75" t="inlineStr"/>
-      <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr">
         <is>
           <t>not_started</t>
@@ -10288,10 +10569,6 @@
           <t>N05</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr"/>
-      <c r="C76" t="inlineStr"/>
-      <c r="D76" t="inlineStr"/>
-      <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr">
         <is>
           <t>not_started</t>
@@ -10304,10 +10581,6 @@
           <t>N06</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr"/>
-      <c r="C77" t="inlineStr"/>
-      <c r="D77" t="inlineStr"/>
-      <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr">
         <is>
           <t>not_started</t>
@@ -10320,10 +10593,6 @@
           <t>N07</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr"/>
-      <c r="C78" t="inlineStr"/>
-      <c r="D78" t="inlineStr"/>
-      <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr">
         <is>
           <t>not_started</t>
@@ -10336,10 +10605,6 @@
           <t>N08</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr"/>
-      <c r="C79" t="inlineStr"/>
-      <c r="D79" t="inlineStr"/>
-      <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr">
         <is>
           <t>not_started</t>
@@ -10352,10 +10617,6 @@
           <t>N09</t>
         </is>
       </c>
-      <c r="B80" t="inlineStr"/>
-      <c r="C80" t="inlineStr"/>
-      <c r="D80" t="inlineStr"/>
-      <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr">
         <is>
           <t>not_started</t>
@@ -10368,10 +10629,6 @@
           <t>ST01</t>
         </is>
       </c>
-      <c r="B81" t="inlineStr"/>
-      <c r="C81" t="inlineStr"/>
-      <c r="D81" t="inlineStr"/>
-      <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr">
         <is>
           <t>not_started</t>
@@ -10384,10 +10641,6 @@
           <t>ST02</t>
         </is>
       </c>
-      <c r="B82" t="inlineStr"/>
-      <c r="C82" t="inlineStr"/>
-      <c r="D82" t="inlineStr"/>
-      <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr">
         <is>
           <t>not_started</t>
@@ -10400,10 +10653,6 @@
           <t>ST03</t>
         </is>
       </c>
-      <c r="B83" t="inlineStr"/>
-      <c r="C83" t="inlineStr"/>
-      <c r="D83" t="inlineStr"/>
-      <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr">
         <is>
           <t>not_started</t>
@@ -10416,10 +10665,6 @@
           <t>ST04</t>
         </is>
       </c>
-      <c r="B84" t="inlineStr"/>
-      <c r="C84" t="inlineStr"/>
-      <c r="D84" t="inlineStr"/>
-      <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr">
         <is>
           <t>not_started</t>
@@ -10432,10 +10677,6 @@
           <t>ST05</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr"/>
-      <c r="C85" t="inlineStr"/>
-      <c r="D85" t="inlineStr"/>
-      <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr">
         <is>
           <t>not_started</t>
@@ -10448,10 +10689,6 @@
           <t>ST06</t>
         </is>
       </c>
-      <c r="B86" t="inlineStr"/>
-      <c r="C86" t="inlineStr"/>
-      <c r="D86" t="inlineStr"/>
-      <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr">
         <is>
           <t>not_started</t>
@@ -10464,10 +10701,6 @@
           <t>ST07</t>
         </is>
       </c>
-      <c r="B87" t="inlineStr"/>
-      <c r="C87" t="inlineStr"/>
-      <c r="D87" t="inlineStr"/>
-      <c r="E87" t="inlineStr"/>
       <c r="F87" t="inlineStr">
         <is>
           <t>not_started</t>
@@ -10480,10 +10713,6 @@
           <t>ST08</t>
         </is>
       </c>
-      <c r="B88" t="inlineStr"/>
-      <c r="C88" t="inlineStr"/>
-      <c r="D88" t="inlineStr"/>
-      <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr">
         <is>
           <t>not_started</t>
@@ -10496,10 +10725,6 @@
           <t>ST09</t>
         </is>
       </c>
-      <c r="B89" t="inlineStr"/>
-      <c r="C89" t="inlineStr"/>
-      <c r="D89" t="inlineStr"/>
-      <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr">
         <is>
           <t>not_started</t>
@@ -10512,10 +10737,6 @@
           <t>ST10</t>
         </is>
       </c>
-      <c r="B90" t="inlineStr"/>
-      <c r="C90" t="inlineStr"/>
-      <c r="D90" t="inlineStr"/>
-      <c r="E90" t="inlineStr"/>
       <c r="F90" t="inlineStr">
         <is>
           <t>not_started</t>
@@ -10528,10 +10749,6 @@
           <t>R01</t>
         </is>
       </c>
-      <c r="B91" t="inlineStr"/>
-      <c r="C91" t="inlineStr"/>
-      <c r="D91" t="inlineStr"/>
-      <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr">
         <is>
           <t>not_started</t>
@@ -10544,10 +10761,6 @@
           <t>R02</t>
         </is>
       </c>
-      <c r="B92" t="inlineStr"/>
-      <c r="C92" t="inlineStr"/>
-      <c r="D92" t="inlineStr"/>
-      <c r="E92" t="inlineStr"/>
       <c r="F92" t="inlineStr">
         <is>
           <t>not_started</t>
@@ -10560,10 +10773,6 @@
           <t>R03</t>
         </is>
       </c>
-      <c r="B93" t="inlineStr"/>
-      <c r="C93" t="inlineStr"/>
-      <c r="D93" t="inlineStr"/>
-      <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr">
         <is>
           <t>not_started</t>
@@ -10576,10 +10785,6 @@
           <t>R04</t>
         </is>
       </c>
-      <c r="B94" t="inlineStr"/>
-      <c r="C94" t="inlineStr"/>
-      <c r="D94" t="inlineStr"/>
-      <c r="E94" t="inlineStr"/>
       <c r="F94" t="inlineStr">
         <is>
           <t>not_started</t>
@@ -10592,10 +10797,6 @@
           <t>R05</t>
         </is>
       </c>
-      <c r="B95" t="inlineStr"/>
-      <c r="C95" t="inlineStr"/>
-      <c r="D95" t="inlineStr"/>
-      <c r="E95" t="inlineStr"/>
       <c r="F95" t="inlineStr">
         <is>
           <t>not_started</t>
@@ -10608,10 +10809,6 @@
           <t>R06</t>
         </is>
       </c>
-      <c r="B96" t="inlineStr"/>
-      <c r="C96" t="inlineStr"/>
-      <c r="D96" t="inlineStr"/>
-      <c r="E96" t="inlineStr"/>
       <c r="F96" t="inlineStr">
         <is>
           <t>not_started</t>
@@ -10624,10 +10821,6 @@
           <t>R07</t>
         </is>
       </c>
-      <c r="B97" t="inlineStr"/>
-      <c r="C97" t="inlineStr"/>
-      <c r="D97" t="inlineStr"/>
-      <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr">
         <is>
           <t>not_started</t>
@@ -10640,10 +10833,6 @@
           <t>R08</t>
         </is>
       </c>
-      <c r="B98" t="inlineStr"/>
-      <c r="C98" t="inlineStr"/>
-      <c r="D98" t="inlineStr"/>
-      <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr">
         <is>
           <t>not_started</t>
@@ -10656,10 +10845,6 @@
           <t>R09</t>
         </is>
       </c>
-      <c r="B99" t="inlineStr"/>
-      <c r="C99" t="inlineStr"/>
-      <c r="D99" t="inlineStr"/>
-      <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr">
         <is>
           <t>not_started</t>
@@ -10672,10 +10857,6 @@
           <t>R10</t>
         </is>
       </c>
-      <c r="B100" t="inlineStr"/>
-      <c r="C100" t="inlineStr"/>
-      <c r="D100" t="inlineStr"/>
-      <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr">
         <is>
           <t>not_started</t>
@@ -10688,10 +10869,6 @@
           <t>F01</t>
         </is>
       </c>
-      <c r="B101" t="inlineStr"/>
-      <c r="C101" t="inlineStr"/>
-      <c r="D101" t="inlineStr"/>
-      <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr">
         <is>
           <t>not_started</t>
@@ -10704,10 +10881,6 @@
           <t>F02</t>
         </is>
       </c>
-      <c r="B102" t="inlineStr"/>
-      <c r="C102" t="inlineStr"/>
-      <c r="D102" t="inlineStr"/>
-      <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr">
         <is>
           <t>not_started</t>
@@ -10720,10 +10893,6 @@
           <t>F03</t>
         </is>
       </c>
-      <c r="B103" t="inlineStr"/>
-      <c r="C103" t="inlineStr"/>
-      <c r="D103" t="inlineStr"/>
-      <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr">
         <is>
           <t>not_started</t>
@@ -10736,10 +10905,6 @@
           <t>F04</t>
         </is>
       </c>
-      <c r="B104" t="inlineStr"/>
-      <c r="C104" t="inlineStr"/>
-      <c r="D104" t="inlineStr"/>
-      <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr">
         <is>
           <t>not_started</t>
@@ -10752,10 +10917,6 @@
           <t>F05</t>
         </is>
       </c>
-      <c r="B105" t="inlineStr"/>
-      <c r="C105" t="inlineStr"/>
-      <c r="D105" t="inlineStr"/>
-      <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr">
         <is>
           <t>not_started</t>
@@ -10768,10 +10929,6 @@
           <t>F06</t>
         </is>
       </c>
-      <c r="B106" t="inlineStr"/>
-      <c r="C106" t="inlineStr"/>
-      <c r="D106" t="inlineStr"/>
-      <c r="E106" t="inlineStr"/>
       <c r="F106" t="inlineStr">
         <is>
           <t>not_started</t>
@@ -10784,10 +10941,6 @@
           <t>F07</t>
         </is>
       </c>
-      <c r="B107" t="inlineStr"/>
-      <c r="C107" t="inlineStr"/>
-      <c r="D107" t="inlineStr"/>
-      <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr">
         <is>
           <t>not_started</t>
@@ -10800,10 +10953,6 @@
           <t>F08</t>
         </is>
       </c>
-      <c r="B108" t="inlineStr"/>
-      <c r="C108" t="inlineStr"/>
-      <c r="D108" t="inlineStr"/>
-      <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr">
         <is>
           <t>not_started</t>
@@ -10816,10 +10965,6 @@
           <t>F09</t>
         </is>
       </c>
-      <c r="B109" t="inlineStr"/>
-      <c r="C109" t="inlineStr"/>
-      <c r="D109" t="inlineStr"/>
-      <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr">
         <is>
           <t>not_started</t>
@@ -10832,10 +10977,6 @@
           <t>SE01</t>
         </is>
       </c>
-      <c r="B110" t="inlineStr"/>
-      <c r="C110" t="inlineStr"/>
-      <c r="D110" t="inlineStr"/>
-      <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr">
         <is>
           <t>not_started</t>
@@ -10848,10 +10989,6 @@
           <t>SE02</t>
         </is>
       </c>
-      <c r="B111" t="inlineStr"/>
-      <c r="C111" t="inlineStr"/>
-      <c r="D111" t="inlineStr"/>
-      <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr">
         <is>
           <t>not_started</t>
@@ -10864,10 +11001,6 @@
           <t>SE03</t>
         </is>
       </c>
-      <c r="B112" t="inlineStr"/>
-      <c r="C112" t="inlineStr"/>
-      <c r="D112" t="inlineStr"/>
-      <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr">
         <is>
           <t>not_started</t>
@@ -10880,10 +11013,6 @@
           <t>SE04</t>
         </is>
       </c>
-      <c r="B113" t="inlineStr"/>
-      <c r="C113" t="inlineStr"/>
-      <c r="D113" t="inlineStr"/>
-      <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr">
         <is>
           <t>not_started</t>
@@ -10896,10 +11025,6 @@
           <t>SE05</t>
         </is>
       </c>
-      <c r="B114" t="inlineStr"/>
-      <c r="C114" t="inlineStr"/>
-      <c r="D114" t="inlineStr"/>
-      <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr">
         <is>
           <t>not_started</t>
@@ -10912,10 +11037,6 @@
           <t>SE06</t>
         </is>
       </c>
-      <c r="B115" t="inlineStr"/>
-      <c r="C115" t="inlineStr"/>
-      <c r="D115" t="inlineStr"/>
-      <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr">
         <is>
           <t>not_started</t>
@@ -10928,10 +11049,6 @@
           <t>SE07</t>
         </is>
       </c>
-      <c r="B116" t="inlineStr"/>
-      <c r="C116" t="inlineStr"/>
-      <c r="D116" t="inlineStr"/>
-      <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr">
         <is>
           <t>not_started</t>
@@ -10944,10 +11061,6 @@
           <t>SE08</t>
         </is>
       </c>
-      <c r="B117" t="inlineStr"/>
-      <c r="C117" t="inlineStr"/>
-      <c r="D117" t="inlineStr"/>
-      <c r="E117" t="inlineStr"/>
       <c r="F117" t="inlineStr">
         <is>
           <t>not_started</t>
@@ -10960,10 +11073,6 @@
           <t>SE09</t>
         </is>
       </c>
-      <c r="B118" t="inlineStr"/>
-      <c r="C118" t="inlineStr"/>
-      <c r="D118" t="inlineStr"/>
-      <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr">
         <is>
           <t>not_started</t>
@@ -10976,10 +11085,6 @@
           <t>SE10</t>
         </is>
       </c>
-      <c r="B119" t="inlineStr"/>
-      <c r="C119" t="inlineStr"/>
-      <c r="D119" t="inlineStr"/>
-      <c r="E119" t="inlineStr"/>
       <c r="F119" t="inlineStr">
         <is>
           <t>not_started</t>
@@ -10992,10 +11097,6 @@
           <t>HY01</t>
         </is>
       </c>
-      <c r="B120" t="inlineStr"/>
-      <c r="C120" t="inlineStr"/>
-      <c r="D120" t="inlineStr"/>
-      <c r="E120" t="inlineStr"/>
       <c r="F120" t="inlineStr">
         <is>
           <t>not_started</t>
@@ -11008,10 +11109,6 @@
           <t>HY02</t>
         </is>
       </c>
-      <c r="B121" t="inlineStr"/>
-      <c r="C121" t="inlineStr"/>
-      <c r="D121" t="inlineStr"/>
-      <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr">
         <is>
           <t>not_started</t>
@@ -11024,10 +11121,6 @@
           <t>HY03</t>
         </is>
       </c>
-      <c r="B122" t="inlineStr"/>
-      <c r="C122" t="inlineStr"/>
-      <c r="D122" t="inlineStr"/>
-      <c r="E122" t="inlineStr"/>
       <c r="F122" t="inlineStr">
         <is>
           <t>not_started</t>
@@ -11040,10 +11133,6 @@
           <t>HY04</t>
         </is>
       </c>
-      <c r="B123" t="inlineStr"/>
-      <c r="C123" t="inlineStr"/>
-      <c r="D123" t="inlineStr"/>
-      <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr">
         <is>
           <t>not_started</t>
@@ -11056,10 +11145,6 @@
           <t>HY05</t>
         </is>
       </c>
-      <c r="B124" t="inlineStr"/>
-      <c r="C124" t="inlineStr"/>
-      <c r="D124" t="inlineStr"/>
-      <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr">
         <is>
           <t>not_started</t>
@@ -11072,10 +11157,6 @@
           <t>HY06</t>
         </is>
       </c>
-      <c r="B125" t="inlineStr"/>
-      <c r="C125" t="inlineStr"/>
-      <c r="D125" t="inlineStr"/>
-      <c r="E125" t="inlineStr"/>
       <c r="F125" t="inlineStr">
         <is>
           <t>not_started</t>
@@ -11088,10 +11169,6 @@
           <t>HY07</t>
         </is>
       </c>
-      <c r="B126" t="inlineStr"/>
-      <c r="C126" t="inlineStr"/>
-      <c r="D126" t="inlineStr"/>
-      <c r="E126" t="inlineStr"/>
       <c r="F126" t="inlineStr">
         <is>
           <t>not_started</t>
@@ -11104,10 +11181,6 @@
           <t>HY08</t>
         </is>
       </c>
-      <c r="B127" t="inlineStr"/>
-      <c r="C127" t="inlineStr"/>
-      <c r="D127" t="inlineStr"/>
-      <c r="E127" t="inlineStr"/>
       <c r="F127" t="inlineStr">
         <is>
           <t>not_started</t>
@@ -11120,10 +11193,6 @@
           <t>HY09</t>
         </is>
       </c>
-      <c r="B128" t="inlineStr"/>
-      <c r="C128" t="inlineStr"/>
-      <c r="D128" t="inlineStr"/>
-      <c r="E128" t="inlineStr"/>
       <c r="F128" t="inlineStr">
         <is>
           <t>not_started</t>
@@ -11136,10 +11205,6 @@
           <t>HW01</t>
         </is>
       </c>
-      <c r="B129" t="inlineStr"/>
-      <c r="C129" t="inlineStr"/>
-      <c r="D129" t="inlineStr"/>
-      <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr">
         <is>
           <t>not_started</t>
@@ -11152,10 +11217,6 @@
           <t>HW02</t>
         </is>
       </c>
-      <c r="B130" t="inlineStr"/>
-      <c r="C130" t="inlineStr"/>
-      <c r="D130" t="inlineStr"/>
-      <c r="E130" t="inlineStr"/>
       <c r="F130" t="inlineStr">
         <is>
           <t>not_started</t>
@@ -11168,10 +11229,6 @@
           <t>HW03</t>
         </is>
       </c>
-      <c r="B131" t="inlineStr"/>
-      <c r="C131" t="inlineStr"/>
-      <c r="D131" t="inlineStr"/>
-      <c r="E131" t="inlineStr"/>
       <c r="F131" t="inlineStr">
         <is>
           <t>not_started</t>
@@ -11184,10 +11241,6 @@
           <t>HW04</t>
         </is>
       </c>
-      <c r="B132" t="inlineStr"/>
-      <c r="C132" t="inlineStr"/>
-      <c r="D132" t="inlineStr"/>
-      <c r="E132" t="inlineStr"/>
       <c r="F132" t="inlineStr">
         <is>
           <t>not_started</t>
@@ -11200,10 +11253,6 @@
           <t>HW05</t>
         </is>
       </c>
-      <c r="B133" t="inlineStr"/>
-      <c r="C133" t="inlineStr"/>
-      <c r="D133" t="inlineStr"/>
-      <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr">
         <is>
           <t>not_started</t>
@@ -11216,10 +11265,6 @@
           <t>HW06</t>
         </is>
       </c>
-      <c r="B134" t="inlineStr"/>
-      <c r="C134" t="inlineStr"/>
-      <c r="D134" t="inlineStr"/>
-      <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr">
         <is>
           <t>not_started</t>
@@ -11232,10 +11277,6 @@
           <t>HW07</t>
         </is>
       </c>
-      <c r="B135" t="inlineStr"/>
-      <c r="C135" t="inlineStr"/>
-      <c r="D135" t="inlineStr"/>
-      <c r="E135" t="inlineStr"/>
       <c r="F135" t="inlineStr">
         <is>
           <t>not_started</t>
@@ -11248,10 +11289,6 @@
           <t>HW08</t>
         </is>
       </c>
-      <c r="B136" t="inlineStr"/>
-      <c r="C136" t="inlineStr"/>
-      <c r="D136" t="inlineStr"/>
-      <c r="E136" t="inlineStr"/>
       <c r="F136" t="inlineStr">
         <is>
           <t>not_started</t>
@@ -11264,10 +11301,6 @@
           <t>QA01</t>
         </is>
       </c>
-      <c r="B137" t="inlineStr"/>
-      <c r="C137" t="inlineStr"/>
-      <c r="D137" t="inlineStr"/>
-      <c r="E137" t="inlineStr"/>
       <c r="F137" t="inlineStr">
         <is>
           <t>not_started</t>
@@ -11280,10 +11313,6 @@
           <t>QA02</t>
         </is>
       </c>
-      <c r="B138" t="inlineStr"/>
-      <c r="C138" t="inlineStr"/>
-      <c r="D138" t="inlineStr"/>
-      <c r="E138" t="inlineStr"/>
       <c r="F138" t="inlineStr">
         <is>
           <t>not_started</t>
@@ -11296,10 +11325,6 @@
           <t>QA03</t>
         </is>
       </c>
-      <c r="B139" t="inlineStr"/>
-      <c r="C139" t="inlineStr"/>
-      <c r="D139" t="inlineStr"/>
-      <c r="E139" t="inlineStr"/>
       <c r="F139" t="inlineStr">
         <is>
           <t>not_started</t>
@@ -11312,10 +11337,6 @@
           <t>QA04</t>
         </is>
       </c>
-      <c r="B140" t="inlineStr"/>
-      <c r="C140" t="inlineStr"/>
-      <c r="D140" t="inlineStr"/>
-      <c r="E140" t="inlineStr"/>
       <c r="F140" t="inlineStr">
         <is>
           <t>not_started</t>
@@ -11328,10 +11349,6 @@
           <t>QA05</t>
         </is>
       </c>
-      <c r="B141" t="inlineStr"/>
-      <c r="C141" t="inlineStr"/>
-      <c r="D141" t="inlineStr"/>
-      <c r="E141" t="inlineStr"/>
       <c r="F141" t="inlineStr">
         <is>
           <t>not_started</t>
@@ -11344,10 +11361,6 @@
           <t>QA06</t>
         </is>
       </c>
-      <c r="B142" t="inlineStr"/>
-      <c r="C142" t="inlineStr"/>
-      <c r="D142" t="inlineStr"/>
-      <c r="E142" t="inlineStr"/>
       <c r="F142" t="inlineStr">
         <is>
           <t>not_started</t>
@@ -11360,10 +11373,6 @@
           <t>QA07</t>
         </is>
       </c>
-      <c r="B143" t="inlineStr"/>
-      <c r="C143" t="inlineStr"/>
-      <c r="D143" t="inlineStr"/>
-      <c r="E143" t="inlineStr"/>
       <c r="F143" t="inlineStr">
         <is>
           <t>not_started</t>
@@ -11376,10 +11385,6 @@
           <t>QA08</t>
         </is>
       </c>
-      <c r="B144" t="inlineStr"/>
-      <c r="C144" t="inlineStr"/>
-      <c r="D144" t="inlineStr"/>
-      <c r="E144" t="inlineStr"/>
       <c r="F144" t="inlineStr">
         <is>
           <t>not_started</t>

--- a/data/cost_forge.xlsx
+++ b/data/cost_forge.xlsx
@@ -7648,7 +7648,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7672,6 +7672,26 @@
           <t>price_eur_per_kg</t>
         </is>
       </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>moq_kg</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>hs_code</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>lead_supplier</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>supplier</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -7692,6 +7712,20 @@
       <c r="D2" t="n">
         <v>14.2</v>
       </c>
+      <c r="E2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>7419.99</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -7712,6 +7746,20 @@
       <c r="D3" t="n">
         <v>16.5</v>
       </c>
+      <c r="E3" t="n">
+        <v>100</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>7419.99</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -7732,6 +7780,20 @@
       <c r="D4" t="n">
         <v>4.8</v>
       </c>
+      <c r="E4" t="n">
+        <v>50</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>7219.31</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -7752,6 +7814,20 @@
       <c r="D5" t="n">
         <v>7.2</v>
       </c>
+      <c r="E5" t="n">
+        <v>50</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>7219.31</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -7772,6 +7848,20 @@
       <c r="D6" t="n">
         <v>22</v>
       </c>
+      <c r="E6" t="n">
+        <v>20</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>7222.20</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -7792,6 +7882,20 @@
       <c r="D7" t="n">
         <v>4.8</v>
       </c>
+      <c r="E7" t="n">
+        <v>25</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>7604.29</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -7812,6 +7916,20 @@
       <c r="D8" t="n">
         <v>5.1</v>
       </c>
+      <c r="E8" t="n">
+        <v>25</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>7606.12</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -7832,6 +7950,20 @@
       <c r="D9" t="n">
         <v>1.35</v>
       </c>
+      <c r="E9" t="n">
+        <v>100</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>7208.51</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -7852,6 +7984,20 @@
       <c r="D10" t="n">
         <v>3.2</v>
       </c>
+      <c r="E10" t="n">
+        <v>10</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>3901.20</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -7872,6 +8018,20 @@
       <c r="D11" t="n">
         <v>8.5</v>
       </c>
+      <c r="E11" t="n">
+        <v>5</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>4016.93</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -7892,6 +8052,20 @@
       <c r="D12" t="n">
         <v>16</v>
       </c>
+      <c r="E12" t="n">
+        <v>5</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>7318.15</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -7912,6 +8086,20 @@
       <c r="D13" t="n">
         <v>30</v>
       </c>
+      <c r="E13" t="n">
+        <v>10</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>8108.20</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Conditional</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -7932,6 +8120,20 @@
       <c r="D14" t="n">
         <v>18</v>
       </c>
+      <c r="E14" t="n">
+        <v>20</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>7219.31</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Conditional</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -7952,6 +8154,20 @@
       <c r="D15" t="n">
         <v>14.5</v>
       </c>
+      <c r="E15" t="n">
+        <v>20</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>7412.20</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -7972,6 +8188,20 @@
       <c r="D16" t="n">
         <v>88</v>
       </c>
+      <c r="E16" t="n">
+        <v>2</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>3909.50</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Sole source</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -7992,6 +8222,20 @@
       <c r="D17" t="n">
         <v>7.2</v>
       </c>
+      <c r="E17" t="n">
+        <v>10</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>7304.41</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8004,7 +8248,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F48"/>
+  <dimension ref="A1:K48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8038,6 +8282,31 @@
           <t>margin_pct</t>
         </is>
       </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>energy_kw</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>rework_pct</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>tooling_consumable_eur_h</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>subcontract_markup_pct</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>labour_grade</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -8062,6 +8331,23 @@
       <c r="F2" t="n">
         <v>0.18</v>
       </c>
+      <c r="G2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="I2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Senior machinist</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -8086,6 +8372,23 @@
       <c r="F3" t="n">
         <v>0.18</v>
       </c>
+      <c r="G3" t="n">
+        <v>18</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="I3" t="n">
+        <v>8</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Senior machinist</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -8110,6 +8413,23 @@
       <c r="F4" t="n">
         <v>0.18</v>
       </c>
+      <c r="G4" t="n">
+        <v>22</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="I4" t="n">
+        <v>8</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Senior machinist</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -8134,6 +8454,23 @@
       <c r="F5" t="n">
         <v>0.18</v>
       </c>
+      <c r="G5" t="n">
+        <v>15</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="I5" t="n">
+        <v>4</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Machinist</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -8158,6 +8495,23 @@
       <c r="F6" t="n">
         <v>0.15</v>
       </c>
+      <c r="G6" t="n">
+        <v>5</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Machinist</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -8182,6 +8536,23 @@
       <c r="F7" t="n">
         <v>0.18</v>
       </c>
+      <c r="G7" t="n">
+        <v>8</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I7" t="n">
+        <v>5</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Certified welder</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -8206,6 +8577,23 @@
       <c r="F8" t="n">
         <v>0.15</v>
       </c>
+      <c r="G8" t="n">
+        <v>35</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="I8" t="n">
+        <v>6</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Operator</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -8230,6 +8618,23 @@
       <c r="F9" t="n">
         <v>0.15</v>
       </c>
+      <c r="G9" t="n">
+        <v>22</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I9" t="n">
+        <v>12</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Operator</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -8254,6 +8659,23 @@
       <c r="F10" t="n">
         <v>0.2</v>
       </c>
+      <c r="G10" t="n">
+        <v>45</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="I10" t="n">
+        <v>3</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Foundry hand</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -8278,6 +8700,23 @@
       <c r="F11" t="n">
         <v>0.15</v>
       </c>
+      <c r="G11" t="n">
+        <v>7</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Test engineer</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -8302,6 +8741,23 @@
       <c r="F12" t="n">
         <v>0.18</v>
       </c>
+      <c r="G12" t="n">
+        <v>3</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Assembly fitter</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -8326,6 +8782,23 @@
       <c r="F13" t="n">
         <v>0.15</v>
       </c>
+      <c r="G13" t="n">
+        <v>4</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I13" t="n">
+        <v>2</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>NDT Level II</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -8350,6 +8823,23 @@
       <c r="F14" t="n">
         <v>0.18</v>
       </c>
+      <c r="G14" t="n">
+        <v>22</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="I14" t="n">
+        <v>10</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Machinist</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -8374,6 +8864,23 @@
       <c r="F15" t="n">
         <v>0.18</v>
       </c>
+      <c r="G15" t="n">
+        <v>40</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="I15" t="n">
+        <v>4</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Plating operator</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -8398,6 +8905,23 @@
       <c r="F16" t="n">
         <v>0.18</v>
       </c>
+      <c r="G16" t="n">
+        <v>35</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="I16" t="n">
+        <v>5</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Plating operator</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -8422,6 +8946,23 @@
       <c r="F17" t="n">
         <v>0.15</v>
       </c>
+      <c r="G17" t="n">
+        <v>20</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="I17" t="n">
+        <v>3</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Coating operator</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -8446,6 +8987,23 @@
       <c r="F18" t="n">
         <v>0.15</v>
       </c>
+      <c r="G18" t="n">
+        <v>30</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="I18" t="n">
+        <v>4</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Coating operator</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -8470,6 +9028,23 @@
       <c r="F19" t="n">
         <v>0.18</v>
       </c>
+      <c r="G19" t="n">
+        <v>15</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="I19" t="n">
+        <v>7</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Machinist</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -8494,6 +9069,23 @@
       <c r="F20" t="n">
         <v>0.18</v>
       </c>
+      <c r="G20" t="n">
+        <v>25</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="I20" t="n">
+        <v>12</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Machinist</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -8518,6 +9110,23 @@
       <c r="F21" t="n">
         <v>0.18</v>
       </c>
+      <c r="G21" t="n">
+        <v>40</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="I21" t="n">
+        <v>14</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Senior machinist</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -8542,6 +9151,23 @@
       <c r="F22" t="n">
         <v>0.18</v>
       </c>
+      <c r="G22" t="n">
+        <v>18</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="I22" t="n">
+        <v>9</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Machinist</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -8566,6 +9192,23 @@
       <c r="F23" t="n">
         <v>0.18</v>
       </c>
+      <c r="G23" t="n">
+        <v>10</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="I23" t="n">
+        <v>4</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Machinist</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -8590,6 +9233,23 @@
       <c r="F24" t="n">
         <v>0.18</v>
       </c>
+      <c r="G24" t="n">
+        <v>7</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="I24" t="n">
+        <v>3</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Senior machinist</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -8614,6 +9274,23 @@
       <c r="F25" t="n">
         <v>0.18</v>
       </c>
+      <c r="G25" t="n">
+        <v>18</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="I25" t="n">
+        <v>8</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Senior machinist</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -8638,6 +9315,23 @@
       <c r="F26" t="n">
         <v>0.18</v>
       </c>
+      <c r="G26" t="n">
+        <v>15</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="I26" t="n">
+        <v>5</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Senior machinist</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -8662,6 +9356,23 @@
       <c r="F27" t="n">
         <v>0.18</v>
       </c>
+      <c r="G27" t="n">
+        <v>22</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="I27" t="n">
+        <v>10</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Senior machinist</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -8686,6 +9397,23 @@
       <c r="F28" t="n">
         <v>0.18</v>
       </c>
+      <c r="G28" t="n">
+        <v>10</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="I28" t="n">
+        <v>5</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Welder</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -8710,6 +9438,23 @@
       <c r="F29" t="n">
         <v>0.18</v>
       </c>
+      <c r="G29" t="n">
+        <v>8</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I29" t="n">
+        <v>5</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Certified welder</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -8734,6 +9479,23 @@
       <c r="F30" t="n">
         <v>0.18</v>
       </c>
+      <c r="G30" t="n">
+        <v>12</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I30" t="n">
+        <v>8</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Certified welder</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -8758,6 +9520,23 @@
       <c r="F31" t="n">
         <v>0.18</v>
       </c>
+      <c r="G31" t="n">
+        <v>25</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="I31" t="n">
+        <v>4</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Laser operator</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -8782,6 +9561,23 @@
       <c r="F32" t="n">
         <v>0.15</v>
       </c>
+      <c r="G32" t="n">
+        <v>30</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I32" t="n">
+        <v>5</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Laser operator</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -8806,6 +9602,23 @@
       <c r="F33" t="n">
         <v>0.15</v>
       </c>
+      <c r="G33" t="n">
+        <v>15</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="I33" t="n">
+        <v>4</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Operator</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -8830,6 +9643,23 @@
       <c r="F34" t="n">
         <v>0.15</v>
       </c>
+      <c r="G34" t="n">
+        <v>22</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="I34" t="n">
+        <v>2</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Operator</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -8854,6 +9684,23 @@
       <c r="F35" t="n">
         <v>0.15</v>
       </c>
+      <c r="G35" t="n">
+        <v>18</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="I35" t="n">
+        <v>2</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Operator</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -8878,6 +9725,23 @@
       <c r="F36" t="n">
         <v>0.2</v>
       </c>
+      <c r="G36" t="n">
+        <v>35</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="I36" t="n">
+        <v>5</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Foundry hand</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -8902,6 +9766,23 @@
       <c r="F37" t="n">
         <v>0.2</v>
       </c>
+      <c r="G37" t="n">
+        <v>30</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="I37" t="n">
+        <v>4</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Foundry hand</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -8926,6 +9807,23 @@
       <c r="F38" t="n">
         <v>0.2</v>
       </c>
+      <c r="G38" t="n">
+        <v>75</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="I38" t="n">
+        <v>3</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Forge operator</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -8950,6 +9848,23 @@
       <c r="F39" t="n">
         <v>0.15</v>
       </c>
+      <c r="G39" t="n">
+        <v>50</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I39" t="n">
+        <v>1</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Operator</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -8974,6 +9889,23 @@
       <c r="F40" t="n">
         <v>0.15</v>
       </c>
+      <c r="G40" t="n">
+        <v>12</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I40" t="n">
+        <v>3</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Operator</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -8998,6 +9930,23 @@
       <c r="F41" t="n">
         <v>0.15</v>
       </c>
+      <c r="G41" t="n">
+        <v>60</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="I41" t="n">
+        <v>2</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Operator</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -9022,6 +9971,23 @@
       <c r="F42" t="n">
         <v>0.18</v>
       </c>
+      <c r="G42" t="n">
+        <v>40</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="I42" t="n">
+        <v>2</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Operator</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -9046,6 +10012,23 @@
       <c r="F43" t="n">
         <v>0.18</v>
       </c>
+      <c r="G43" t="n">
+        <v>15</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="I43" t="n">
+        <v>2</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Operator</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -9070,6 +10053,23 @@
       <c r="F44" t="n">
         <v>0.15</v>
       </c>
+      <c r="G44" t="n">
+        <v>3</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Metrology technician</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -9094,6 +10094,23 @@
       <c r="F45" t="n">
         <v>0.15</v>
       </c>
+      <c r="G45" t="n">
+        <v>15</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I45" t="n">
+        <v>2</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>RT Level II</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -9118,6 +10135,23 @@
       <c r="F46" t="n">
         <v>0.15</v>
       </c>
+      <c r="G46" t="n">
+        <v>10</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I46" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Test engineer</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -9142,6 +10176,23 @@
       <c r="F47" t="n">
         <v>0.15</v>
       </c>
+      <c r="G47" t="n">
+        <v>5</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I47" t="n">
+        <v>2</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Test engineer</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -9165,6 +10216,23 @@
       </c>
       <c r="F48" t="n">
         <v>0.15</v>
+      </c>
+      <c r="G48" t="n">
+        <v>8</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I48" t="n">
+        <v>1</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Test engineer</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/data/cost_forge.xlsx
+++ b/data/cost_forge.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M144"/>
+  <dimension ref="A1:O144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,6 +486,16 @@
           <t>scale_exp</t>
         </is>
       </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>pattern_cost_eur</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>pattern_amort_qty</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -533,9 +543,16 @@
           <t>UNIT</t>
         </is>
       </c>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
         <v>3</v>
       </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -583,9 +600,16 @@
           <t>UNIT</t>
         </is>
       </c>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
         <v>2</v>
       </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -633,9 +657,16 @@
           <t>UNIT</t>
         </is>
       </c>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
         <v>2</v>
       </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -683,9 +714,16 @@
           <t>UNIT</t>
         </is>
       </c>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
         <v>2</v>
       </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -733,9 +771,16 @@
           <t>UNIT</t>
         </is>
       </c>
+      <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
         <v>2</v>
       </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -783,8 +828,15 @@
           <t>UNIT</t>
         </is>
       </c>
+      <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
         <v>1</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -833,9 +885,16 @@
           <t>UNIT</t>
         </is>
       </c>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
         <v>2</v>
       </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -883,8 +942,15 @@
           <t>UNIT</t>
         </is>
       </c>
+      <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
         <v>1</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -933,7 +999,14 @@
           <t>UNIT</t>
         </is>
       </c>
+      <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -983,7 +1056,14 @@
           <t>UNIT</t>
         </is>
       </c>
+      <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1033,7 +1113,14 @@
           <t>UNIT</t>
         </is>
       </c>
+      <c r="L12" t="inlineStr"/>
       <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1083,7 +1170,14 @@
           <t>UNIT</t>
         </is>
       </c>
+      <c r="L13" t="inlineStr"/>
       <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1115,27 +1209,36 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
         <v>0.6</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
           <t>UNIT</t>
         </is>
+      </c>
+      <c r="L14" t="n">
+        <v>3500</v>
       </c>
       <c r="M14" t="n">
         <v>3</v>
       </c>
+      <c r="N14" t="n">
+        <v>15000</v>
+      </c>
+      <c r="O14" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1183,9 +1286,16 @@
           <t>UNIT</t>
         </is>
       </c>
+      <c r="L15" t="inlineStr"/>
       <c r="M15" t="n">
         <v>2</v>
       </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1233,9 +1343,16 @@
           <t>UNIT</t>
         </is>
       </c>
+      <c r="L16" t="inlineStr"/>
       <c r="M16" t="n">
         <v>2</v>
       </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1283,9 +1400,16 @@
           <t>UNIT</t>
         </is>
       </c>
+      <c r="L17" t="inlineStr"/>
       <c r="M17" t="n">
         <v>2</v>
       </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1333,9 +1457,16 @@
           <t>UNIT</t>
         </is>
       </c>
+      <c r="L18" t="inlineStr"/>
       <c r="M18" t="n">
         <v>2</v>
       </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1383,8 +1514,15 @@
           <t>UNIT</t>
         </is>
       </c>
+      <c r="L19" t="inlineStr"/>
       <c r="M19" t="n">
         <v>1</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1433,7 +1571,14 @@
           <t>UNIT</t>
         </is>
       </c>
+      <c r="L20" t="inlineStr"/>
       <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1483,9 +1628,16 @@
           <t>UNIT</t>
         </is>
       </c>
+      <c r="L21" t="inlineStr"/>
       <c r="M21" t="n">
         <v>2</v>
       </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1533,7 +1685,14 @@
           <t>UNIT</t>
         </is>
       </c>
+      <c r="L22" t="inlineStr"/>
       <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1583,7 +1742,14 @@
           <t>UNIT</t>
         </is>
       </c>
+      <c r="L23" t="inlineStr"/>
       <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1615,27 +1781,36 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
         <v>0.6</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
           <t>UNIT</t>
         </is>
+      </c>
+      <c r="L24" t="n">
+        <v>5200</v>
       </c>
       <c r="M24" t="n">
         <v>3</v>
       </c>
+      <c r="N24" t="n">
+        <v>18000</v>
+      </c>
+      <c r="O24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1665,27 +1840,36 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I25" t="n">
         <v>0.6</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
           <t>UNIT</t>
         </is>
+      </c>
+      <c r="L25" t="n">
+        <v>2100</v>
       </c>
       <c r="M25" t="n">
         <v>3</v>
       </c>
+      <c r="N25" t="n">
+        <v>12000</v>
+      </c>
+      <c r="O25" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1733,9 +1917,16 @@
           <t>UNIT</t>
         </is>
       </c>
+      <c r="L26" t="inlineStr"/>
       <c r="M26" t="n">
         <v>2</v>
       </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1783,7 +1974,14 @@
           <t>UNIT</t>
         </is>
       </c>
+      <c r="L27" t="inlineStr"/>
       <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1833,9 +2031,16 @@
           <t>UNIT</t>
         </is>
       </c>
+      <c r="L28" t="inlineStr"/>
       <c r="M28" t="n">
         <v>2</v>
       </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1883,9 +2088,16 @@
           <t>UNIT</t>
         </is>
       </c>
+      <c r="L29" t="inlineStr"/>
       <c r="M29" t="n">
         <v>2</v>
       </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1933,9 +2145,16 @@
           <t>UNIT</t>
         </is>
       </c>
+      <c r="L30" t="inlineStr"/>
       <c r="M30" t="n">
         <v>2</v>
       </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1983,9 +2202,16 @@
           <t>UNIT</t>
         </is>
       </c>
+      <c r="L31" t="inlineStr"/>
       <c r="M31" t="n">
         <v>2</v>
       </c>
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2033,8 +2259,15 @@
           <t>UNIT</t>
         </is>
       </c>
+      <c r="L32" t="inlineStr"/>
       <c r="M32" t="n">
         <v>1</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -2083,8 +2316,15 @@
           <t>UNIT</t>
         </is>
       </c>
+      <c r="L33" t="inlineStr"/>
       <c r="M33" t="n">
         <v>1</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -2133,7 +2373,14 @@
           <t>UNIT</t>
         </is>
       </c>
+      <c r="L34" t="inlineStr"/>
       <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2183,7 +2430,14 @@
           <t>UNIT</t>
         </is>
       </c>
+      <c r="L35" t="inlineStr"/>
       <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2233,7 +2487,14 @@
           <t>UNIT</t>
         </is>
       </c>
+      <c r="L36" t="inlineStr"/>
       <c r="M36" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2283,9 +2544,16 @@
           <t>UNIT</t>
         </is>
       </c>
+      <c r="L37" t="inlineStr"/>
       <c r="M37" t="n">
         <v>2</v>
       </c>
+      <c r="N37" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2333,7 +2601,14 @@
           <t>UNIT</t>
         </is>
       </c>
+      <c r="L38" t="inlineStr"/>
       <c r="M38" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2383,9 +2658,16 @@
           <t>UNIT</t>
         </is>
       </c>
+      <c r="L39" t="inlineStr"/>
       <c r="M39" t="n">
         <v>2</v>
       </c>
+      <c r="N39" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2433,9 +2715,16 @@
           <t>UNIT</t>
         </is>
       </c>
+      <c r="L40" t="inlineStr"/>
       <c r="M40" t="n">
         <v>2</v>
       </c>
+      <c r="N40" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2483,9 +2772,16 @@
           <t>UNIT</t>
         </is>
       </c>
+      <c r="L41" t="inlineStr"/>
       <c r="M41" t="n">
         <v>2</v>
       </c>
+      <c r="N41" t="n">
+        <v>0</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2533,9 +2829,16 @@
           <t>UNIT</t>
         </is>
       </c>
+      <c r="L42" t="inlineStr"/>
       <c r="M42" t="n">
         <v>2</v>
       </c>
+      <c r="N42" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2583,9 +2886,16 @@
           <t>UNIT</t>
         </is>
       </c>
+      <c r="L43" t="inlineStr"/>
       <c r="M43" t="n">
         <v>2</v>
       </c>
+      <c r="N43" t="n">
+        <v>0</v>
+      </c>
+      <c r="O43" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2633,9 +2943,16 @@
           <t>UNIT</t>
         </is>
       </c>
+      <c r="L44" t="inlineStr"/>
       <c r="M44" t="n">
         <v>2</v>
       </c>
+      <c r="N44" t="n">
+        <v>0</v>
+      </c>
+      <c r="O44" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2683,8 +3000,15 @@
           <t>UNIT</t>
         </is>
       </c>
+      <c r="L45" t="inlineStr"/>
       <c r="M45" t="n">
         <v>1</v>
+      </c>
+      <c r="N45" t="n">
+        <v>0</v>
+      </c>
+      <c r="O45" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -2733,7 +3057,14 @@
           <t>UNIT</t>
         </is>
       </c>
+      <c r="L46" t="inlineStr"/>
       <c r="M46" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2783,8 +3114,15 @@
           <t>UNIT</t>
         </is>
       </c>
+      <c r="L47" t="inlineStr"/>
       <c r="M47" t="n">
         <v>1</v>
+      </c>
+      <c r="N47" t="n">
+        <v>0</v>
+      </c>
+      <c r="O47" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -2833,7 +3171,14 @@
           <t>UNIT</t>
         </is>
       </c>
+      <c r="L48" t="inlineStr"/>
       <c r="M48" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" t="n">
+        <v>0</v>
+      </c>
+      <c r="O48" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2883,7 +3228,14 @@
           <t>UNIT</t>
         </is>
       </c>
+      <c r="L49" t="inlineStr"/>
       <c r="M49" t="n">
+        <v>0</v>
+      </c>
+      <c r="N49" t="n">
+        <v>0</v>
+      </c>
+      <c r="O49" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2933,7 +3285,14 @@
           <t>UNIT</t>
         </is>
       </c>
+      <c r="L50" t="inlineStr"/>
       <c r="M50" t="n">
+        <v>0</v>
+      </c>
+      <c r="N50" t="n">
+        <v>0</v>
+      </c>
+      <c r="O50" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2983,9 +3342,16 @@
           <t>UNIT</t>
         </is>
       </c>
+      <c r="L51" t="inlineStr"/>
       <c r="M51" t="n">
         <v>2</v>
       </c>
+      <c r="N51" t="n">
+        <v>0</v>
+      </c>
+      <c r="O51" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -3033,9 +3399,16 @@
           <t>UNIT</t>
         </is>
       </c>
+      <c r="L52" t="inlineStr"/>
       <c r="M52" t="n">
         <v>2</v>
       </c>
+      <c r="N52" t="n">
+        <v>0</v>
+      </c>
+      <c r="O52" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3083,9 +3456,16 @@
           <t>UNIT</t>
         </is>
       </c>
+      <c r="L53" t="inlineStr"/>
       <c r="M53" t="n">
         <v>2</v>
       </c>
+      <c r="N53" t="n">
+        <v>0</v>
+      </c>
+      <c r="O53" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3133,7 +3513,14 @@
           <t>UNIT</t>
         </is>
       </c>
+      <c r="L54" t="inlineStr"/>
       <c r="M54" t="n">
+        <v>0</v>
+      </c>
+      <c r="N54" t="n">
+        <v>0</v>
+      </c>
+      <c r="O54" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3183,8 +3570,15 @@
           <t>UNIT</t>
         </is>
       </c>
+      <c r="L55" t="inlineStr"/>
       <c r="M55" t="n">
         <v>1</v>
+      </c>
+      <c r="N55" t="n">
+        <v>0</v>
+      </c>
+      <c r="O55" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -3233,9 +3627,16 @@
           <t>UNIT</t>
         </is>
       </c>
+      <c r="L56" t="inlineStr"/>
       <c r="M56" t="n">
         <v>2</v>
       </c>
+      <c r="N56" t="n">
+        <v>0</v>
+      </c>
+      <c r="O56" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3283,8 +3684,15 @@
           <t>UNIT</t>
         </is>
       </c>
+      <c r="L57" t="inlineStr"/>
       <c r="M57" t="n">
         <v>1</v>
+      </c>
+      <c r="N57" t="n">
+        <v>0</v>
+      </c>
+      <c r="O57" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -3333,7 +3741,14 @@
           <t>UNIT</t>
         </is>
       </c>
+      <c r="L58" t="inlineStr"/>
       <c r="M58" t="n">
+        <v>0</v>
+      </c>
+      <c r="N58" t="n">
+        <v>0</v>
+      </c>
+      <c r="O58" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3383,7 +3798,14 @@
           <t>UNIT</t>
         </is>
       </c>
+      <c r="L59" t="inlineStr"/>
       <c r="M59" t="n">
+        <v>0</v>
+      </c>
+      <c r="N59" t="n">
+        <v>0</v>
+      </c>
+      <c r="O59" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3433,7 +3855,14 @@
           <t>UNIT</t>
         </is>
       </c>
+      <c r="L60" t="inlineStr"/>
       <c r="M60" t="n">
+        <v>0</v>
+      </c>
+      <c r="N60" t="n">
+        <v>0</v>
+      </c>
+      <c r="O60" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3483,9 +3912,16 @@
           <t>UNIT</t>
         </is>
       </c>
+      <c r="L61" t="inlineStr"/>
       <c r="M61" t="n">
         <v>2</v>
       </c>
+      <c r="N61" t="n">
+        <v>0</v>
+      </c>
+      <c r="O61" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -3533,9 +3969,16 @@
           <t>UNIT</t>
         </is>
       </c>
+      <c r="L62" t="inlineStr"/>
       <c r="M62" t="n">
         <v>2</v>
       </c>
+      <c r="N62" t="n">
+        <v>0</v>
+      </c>
+      <c r="O62" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -3583,9 +4026,16 @@
           <t>UNIT</t>
         </is>
       </c>
+      <c r="L63" t="inlineStr"/>
       <c r="M63" t="n">
         <v>2</v>
       </c>
+      <c r="N63" t="n">
+        <v>0</v>
+      </c>
+      <c r="O63" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -3633,9 +4083,16 @@
           <t>UNIT</t>
         </is>
       </c>
+      <c r="L64" t="inlineStr"/>
       <c r="M64" t="n">
         <v>2</v>
       </c>
+      <c r="N64" t="n">
+        <v>0</v>
+      </c>
+      <c r="O64" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -3683,9 +4140,16 @@
           <t>UNIT</t>
         </is>
       </c>
+      <c r="L65" t="inlineStr"/>
       <c r="M65" t="n">
         <v>2</v>
       </c>
+      <c r="N65" t="n">
+        <v>0</v>
+      </c>
+      <c r="O65" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -3733,9 +4197,16 @@
           <t>UNIT</t>
         </is>
       </c>
+      <c r="L66" t="inlineStr"/>
       <c r="M66" t="n">
         <v>2</v>
       </c>
+      <c r="N66" t="n">
+        <v>0</v>
+      </c>
+      <c r="O66" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -3783,9 +4254,16 @@
           <t>UNIT</t>
         </is>
       </c>
+      <c r="L67" t="inlineStr"/>
       <c r="M67" t="n">
         <v>2</v>
       </c>
+      <c r="N67" t="n">
+        <v>0</v>
+      </c>
+      <c r="O67" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -3833,8 +4311,15 @@
           <t>UNIT</t>
         </is>
       </c>
+      <c r="L68" t="inlineStr"/>
       <c r="M68" t="n">
         <v>1</v>
+      </c>
+      <c r="N68" t="n">
+        <v>0</v>
+      </c>
+      <c r="O68" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -3883,7 +4368,14 @@
           <t>UNIT</t>
         </is>
       </c>
+      <c r="L69" t="inlineStr"/>
       <c r="M69" t="n">
+        <v>0</v>
+      </c>
+      <c r="N69" t="n">
+        <v>0</v>
+      </c>
+      <c r="O69" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3933,7 +4425,14 @@
           <t>UNIT</t>
         </is>
       </c>
+      <c r="L70" t="inlineStr"/>
       <c r="M70" t="n">
+        <v>0</v>
+      </c>
+      <c r="N70" t="n">
+        <v>0</v>
+      </c>
+      <c r="O70" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3983,7 +4482,14 @@
           <t>UNIT</t>
         </is>
       </c>
+      <c r="L71" t="inlineStr"/>
       <c r="M71" t="n">
+        <v>0</v>
+      </c>
+      <c r="N71" t="n">
+        <v>0</v>
+      </c>
+      <c r="O71" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4033,9 +4539,16 @@
           <t>UNIT</t>
         </is>
       </c>
+      <c r="L72" t="inlineStr"/>
       <c r="M72" t="n">
         <v>2</v>
       </c>
+      <c r="N72" t="n">
+        <v>0</v>
+      </c>
+      <c r="O72" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -4083,9 +4596,16 @@
           <t>UNIT</t>
         </is>
       </c>
+      <c r="L73" t="inlineStr"/>
       <c r="M73" t="n">
         <v>2</v>
       </c>
+      <c r="N73" t="n">
+        <v>0</v>
+      </c>
+      <c r="O73" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -4133,9 +4653,16 @@
           <t>UNIT</t>
         </is>
       </c>
+      <c r="L74" t="inlineStr"/>
       <c r="M74" t="n">
         <v>2</v>
       </c>
+      <c r="N74" t="n">
+        <v>0</v>
+      </c>
+      <c r="O74" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -4183,9 +4710,16 @@
           <t>UNIT</t>
         </is>
       </c>
+      <c r="L75" t="inlineStr"/>
       <c r="M75" t="n">
         <v>2</v>
       </c>
+      <c r="N75" t="n">
+        <v>0</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -4233,8 +4767,15 @@
           <t>UNIT</t>
         </is>
       </c>
+      <c r="L76" t="inlineStr"/>
       <c r="M76" t="n">
         <v>1</v>
+      </c>
+      <c r="N76" t="n">
+        <v>0</v>
+      </c>
+      <c r="O76" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="77">
@@ -4283,8 +4824,15 @@
           <t>UNIT</t>
         </is>
       </c>
+      <c r="L77" t="inlineStr"/>
       <c r="M77" t="n">
         <v>1</v>
+      </c>
+      <c r="N77" t="n">
+        <v>0</v>
+      </c>
+      <c r="O77" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="78">
@@ -4333,7 +4881,14 @@
           <t>UNIT</t>
         </is>
       </c>
+      <c r="L78" t="inlineStr"/>
       <c r="M78" t="n">
+        <v>0</v>
+      </c>
+      <c r="N78" t="n">
+        <v>0</v>
+      </c>
+      <c r="O78" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4383,7 +4938,14 @@
           <t>UNIT</t>
         </is>
       </c>
+      <c r="L79" t="inlineStr"/>
       <c r="M79" t="n">
+        <v>0</v>
+      </c>
+      <c r="N79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O79" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4433,7 +4995,14 @@
           <t>UNIT</t>
         </is>
       </c>
+      <c r="L80" t="inlineStr"/>
       <c r="M80" t="n">
+        <v>0</v>
+      </c>
+      <c r="N80" t="n">
+        <v>0</v>
+      </c>
+      <c r="O80" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4483,9 +5052,16 @@
           <t>UNIT</t>
         </is>
       </c>
+      <c r="L81" t="inlineStr"/>
       <c r="M81" t="n">
         <v>2</v>
       </c>
+      <c r="N81" t="n">
+        <v>0</v>
+      </c>
+      <c r="O81" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -4533,9 +5109,16 @@
           <t>UNIT</t>
         </is>
       </c>
+      <c r="L82" t="inlineStr"/>
       <c r="M82" t="n">
         <v>2</v>
       </c>
+      <c r="N82" t="n">
+        <v>0</v>
+      </c>
+      <c r="O82" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -4583,9 +5166,16 @@
           <t>UNIT</t>
         </is>
       </c>
+      <c r="L83" t="inlineStr"/>
       <c r="M83" t="n">
         <v>2</v>
       </c>
+      <c r="N83" t="n">
+        <v>0</v>
+      </c>
+      <c r="O83" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -4633,9 +5223,16 @@
           <t>UNIT</t>
         </is>
       </c>
+      <c r="L84" t="inlineStr"/>
       <c r="M84" t="n">
         <v>2</v>
       </c>
+      <c r="N84" t="n">
+        <v>0</v>
+      </c>
+      <c r="O84" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -4683,9 +5280,16 @@
           <t>UNIT</t>
         </is>
       </c>
+      <c r="L85" t="inlineStr"/>
       <c r="M85" t="n">
         <v>2</v>
       </c>
+      <c r="N85" t="n">
+        <v>0</v>
+      </c>
+      <c r="O85" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -4733,9 +5337,16 @@
           <t>UNIT</t>
         </is>
       </c>
+      <c r="L86" t="inlineStr"/>
       <c r="M86" t="n">
         <v>2</v>
       </c>
+      <c r="N86" t="n">
+        <v>0</v>
+      </c>
+      <c r="O86" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -4783,8 +5394,15 @@
           <t>UNIT</t>
         </is>
       </c>
+      <c r="L87" t="inlineStr"/>
       <c r="M87" t="n">
         <v>1</v>
+      </c>
+      <c r="N87" t="n">
+        <v>0</v>
+      </c>
+      <c r="O87" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="88">
@@ -4833,8 +5451,15 @@
           <t>UNIT</t>
         </is>
       </c>
+      <c r="L88" t="inlineStr"/>
       <c r="M88" t="n">
         <v>1</v>
+      </c>
+      <c r="N88" t="n">
+        <v>0</v>
+      </c>
+      <c r="O88" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="89">
@@ -4883,8 +5508,15 @@
           <t>UNIT</t>
         </is>
       </c>
+      <c r="L89" t="inlineStr"/>
       <c r="M89" t="n">
         <v>1</v>
+      </c>
+      <c r="N89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O89" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="90">
@@ -4933,7 +5565,14 @@
           <t>UNIT</t>
         </is>
       </c>
+      <c r="L90" t="inlineStr"/>
       <c r="M90" t="n">
+        <v>0</v>
+      </c>
+      <c r="N90" t="n">
+        <v>0</v>
+      </c>
+      <c r="O90" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4983,9 +5622,16 @@
           <t>UNIT</t>
         </is>
       </c>
+      <c r="L91" t="inlineStr"/>
       <c r="M91" t="n">
         <v>2</v>
       </c>
+      <c r="N91" t="n">
+        <v>0</v>
+      </c>
+      <c r="O91" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -5033,9 +5679,16 @@
           <t>UNIT</t>
         </is>
       </c>
+      <c r="L92" t="inlineStr"/>
       <c r="M92" t="n">
         <v>2</v>
       </c>
+      <c r="N92" t="n">
+        <v>0</v>
+      </c>
+      <c r="O92" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -5083,8 +5736,15 @@
           <t>UNIT</t>
         </is>
       </c>
+      <c r="L93" t="inlineStr"/>
       <c r="M93" t="n">
         <v>1</v>
+      </c>
+      <c r="N93" t="n">
+        <v>0</v>
+      </c>
+      <c r="O93" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="94">
@@ -5133,9 +5793,16 @@
           <t>UNIT</t>
         </is>
       </c>
+      <c r="L94" t="inlineStr"/>
       <c r="M94" t="n">
         <v>2</v>
       </c>
+      <c r="N94" t="n">
+        <v>0</v>
+      </c>
+      <c r="O94" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -5183,9 +5850,16 @@
           <t>UNIT</t>
         </is>
       </c>
+      <c r="L95" t="inlineStr"/>
       <c r="M95" t="n">
         <v>2</v>
       </c>
+      <c r="N95" t="n">
+        <v>0</v>
+      </c>
+      <c r="O95" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -5233,8 +5907,15 @@
           <t>UNIT</t>
         </is>
       </c>
+      <c r="L96" t="inlineStr"/>
       <c r="M96" t="n">
         <v>1</v>
+      </c>
+      <c r="N96" t="n">
+        <v>0</v>
+      </c>
+      <c r="O96" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="97">
@@ -5283,8 +5964,15 @@
           <t>UNIT</t>
         </is>
       </c>
+      <c r="L97" t="inlineStr"/>
       <c r="M97" t="n">
         <v>1</v>
+      </c>
+      <c r="N97" t="n">
+        <v>0</v>
+      </c>
+      <c r="O97" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="98">
@@ -5333,8 +6021,15 @@
           <t>UNIT</t>
         </is>
       </c>
+      <c r="L98" t="inlineStr"/>
       <c r="M98" t="n">
         <v>1</v>
+      </c>
+      <c r="N98" t="n">
+        <v>0</v>
+      </c>
+      <c r="O98" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="99">
@@ -5383,7 +6078,14 @@
           <t>UNIT</t>
         </is>
       </c>
+      <c r="L99" t="inlineStr"/>
       <c r="M99" t="n">
+        <v>0</v>
+      </c>
+      <c r="N99" t="n">
+        <v>0</v>
+      </c>
+      <c r="O99" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5433,7 +6135,14 @@
           <t>UNIT</t>
         </is>
       </c>
+      <c r="L100" t="inlineStr"/>
       <c r="M100" t="n">
+        <v>0</v>
+      </c>
+      <c r="N100" t="n">
+        <v>0</v>
+      </c>
+      <c r="O100" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5483,9 +6192,16 @@
           <t>UNIT</t>
         </is>
       </c>
+      <c r="L101" t="inlineStr"/>
       <c r="M101" t="n">
         <v>2</v>
       </c>
+      <c r="N101" t="n">
+        <v>0</v>
+      </c>
+      <c r="O101" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -5533,9 +6249,16 @@
           <t>UNIT</t>
         </is>
       </c>
+      <c r="L102" t="inlineStr"/>
       <c r="M102" t="n">
         <v>2</v>
       </c>
+      <c r="N102" t="n">
+        <v>0</v>
+      </c>
+      <c r="O102" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -5583,9 +6306,16 @@
           <t>UNIT</t>
         </is>
       </c>
+      <c r="L103" t="inlineStr"/>
       <c r="M103" t="n">
         <v>2</v>
       </c>
+      <c r="N103" t="n">
+        <v>0</v>
+      </c>
+      <c r="O103" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -5633,9 +6363,16 @@
           <t>UNIT</t>
         </is>
       </c>
+      <c r="L104" t="inlineStr"/>
       <c r="M104" t="n">
         <v>2</v>
       </c>
+      <c r="N104" t="n">
+        <v>0</v>
+      </c>
+      <c r="O104" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -5683,9 +6420,16 @@
           <t>UNIT</t>
         </is>
       </c>
+      <c r="L105" t="inlineStr"/>
       <c r="M105" t="n">
         <v>2</v>
       </c>
+      <c r="N105" t="n">
+        <v>0</v>
+      </c>
+      <c r="O105" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -5733,9 +6477,16 @@
           <t>UNIT</t>
         </is>
       </c>
+      <c r="L106" t="inlineStr"/>
       <c r="M106" t="n">
         <v>2</v>
       </c>
+      <c r="N106" t="n">
+        <v>0</v>
+      </c>
+      <c r="O106" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -5783,7 +6534,14 @@
           <t>UNIT</t>
         </is>
       </c>
+      <c r="L107" t="inlineStr"/>
       <c r="M107" t="n">
+        <v>0</v>
+      </c>
+      <c r="N107" t="n">
+        <v>0</v>
+      </c>
+      <c r="O107" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5833,9 +6591,16 @@
           <t>UNIT</t>
         </is>
       </c>
+      <c r="L108" t="inlineStr"/>
       <c r="M108" t="n">
         <v>2</v>
       </c>
+      <c r="N108" t="n">
+        <v>0</v>
+      </c>
+      <c r="O108" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -5883,7 +6648,14 @@
           <t>UNIT</t>
         </is>
       </c>
+      <c r="L109" t="inlineStr"/>
       <c r="M109" t="n">
+        <v>0</v>
+      </c>
+      <c r="N109" t="n">
+        <v>0</v>
+      </c>
+      <c r="O109" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5933,9 +6705,16 @@
           <t>UNIT</t>
         </is>
       </c>
+      <c r="L110" t="inlineStr"/>
       <c r="M110" t="n">
         <v>2</v>
       </c>
+      <c r="N110" t="n">
+        <v>0</v>
+      </c>
+      <c r="O110" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -5983,9 +6762,16 @@
           <t>UNIT</t>
         </is>
       </c>
+      <c r="L111" t="inlineStr"/>
       <c r="M111" t="n">
         <v>2</v>
       </c>
+      <c r="N111" t="n">
+        <v>0</v>
+      </c>
+      <c r="O111" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -6033,7 +6819,14 @@
           <t>UNIT</t>
         </is>
       </c>
+      <c r="L112" t="inlineStr"/>
       <c r="M112" t="n">
+        <v>0</v>
+      </c>
+      <c r="N112" t="n">
+        <v>0</v>
+      </c>
+      <c r="O112" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6083,8 +6876,15 @@
           <t>UNIT</t>
         </is>
       </c>
+      <c r="L113" t="inlineStr"/>
       <c r="M113" t="n">
         <v>1</v>
+      </c>
+      <c r="N113" t="n">
+        <v>0</v>
+      </c>
+      <c r="O113" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="114">
@@ -6133,8 +6933,15 @@
           <t>UNIT</t>
         </is>
       </c>
+      <c r="L114" t="inlineStr"/>
       <c r="M114" t="n">
         <v>1</v>
+      </c>
+      <c r="N114" t="n">
+        <v>0</v>
+      </c>
+      <c r="O114" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="115">
@@ -6183,8 +6990,15 @@
           <t>UNIT</t>
         </is>
       </c>
+      <c r="L115" t="inlineStr"/>
       <c r="M115" t="n">
         <v>1</v>
+      </c>
+      <c r="N115" t="n">
+        <v>0</v>
+      </c>
+      <c r="O115" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="116">
@@ -6233,8 +7047,15 @@
           <t>UNIT</t>
         </is>
       </c>
+      <c r="L116" t="inlineStr"/>
       <c r="M116" t="n">
         <v>1</v>
+      </c>
+      <c r="N116" t="n">
+        <v>0</v>
+      </c>
+      <c r="O116" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="117">
@@ -6283,9 +7104,16 @@
           <t>UNIT</t>
         </is>
       </c>
+      <c r="L117" t="inlineStr"/>
       <c r="M117" t="n">
         <v>2</v>
       </c>
+      <c r="N117" t="n">
+        <v>0</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -6333,7 +7161,14 @@
           <t>UNIT</t>
         </is>
       </c>
+      <c r="L118" t="inlineStr"/>
       <c r="M118" t="n">
+        <v>0</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0</v>
+      </c>
+      <c r="O118" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6383,7 +7218,14 @@
           <t>UNIT</t>
         </is>
       </c>
+      <c r="L119" t="inlineStr"/>
       <c r="M119" t="n">
+        <v>0</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0</v>
+      </c>
+      <c r="O119" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6433,8 +7275,15 @@
           <t>UNIT</t>
         </is>
       </c>
+      <c r="L120" t="inlineStr"/>
       <c r="M120" t="n">
         <v>1</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="121">
@@ -6483,8 +7332,15 @@
           <t>UNIT</t>
         </is>
       </c>
+      <c r="L121" t="inlineStr"/>
       <c r="M121" t="n">
         <v>1</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="122">
@@ -6533,8 +7389,15 @@
           <t>UNIT</t>
         </is>
       </c>
+      <c r="L122" t="inlineStr"/>
       <c r="M122" t="n">
         <v>1</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="123">
@@ -6583,8 +7446,15 @@
           <t>UNIT</t>
         </is>
       </c>
+      <c r="L123" t="inlineStr"/>
       <c r="M123" t="n">
         <v>1</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="124">
@@ -6633,8 +7503,15 @@
           <t>UNIT</t>
         </is>
       </c>
+      <c r="L124" t="inlineStr"/>
       <c r="M124" t="n">
         <v>1</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="125">
@@ -6683,8 +7560,15 @@
           <t>UNIT</t>
         </is>
       </c>
+      <c r="L125" t="inlineStr"/>
       <c r="M125" t="n">
         <v>1</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="126">
@@ -6733,8 +7617,15 @@
           <t>UNIT</t>
         </is>
       </c>
+      <c r="L126" t="inlineStr"/>
       <c r="M126" t="n">
         <v>1</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="127">
@@ -6783,7 +7674,14 @@
           <t>UNIT</t>
         </is>
       </c>
+      <c r="L127" t="inlineStr"/>
       <c r="M127" t="n">
+        <v>0</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0</v>
+      </c>
+      <c r="O127" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6833,7 +7731,14 @@
           <t>UNIT</t>
         </is>
       </c>
+      <c r="L128" t="inlineStr"/>
       <c r="M128" t="n">
+        <v>0</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0</v>
+      </c>
+      <c r="O128" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6883,7 +7788,14 @@
           <t>UNIT</t>
         </is>
       </c>
+      <c r="L129" t="inlineStr"/>
       <c r="M129" t="n">
+        <v>0</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0</v>
+      </c>
+      <c r="O129" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6933,7 +7845,14 @@
           <t>UNIT</t>
         </is>
       </c>
+      <c r="L130" t="inlineStr"/>
       <c r="M130" t="n">
+        <v>0</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0</v>
+      </c>
+      <c r="O130" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6983,7 +7902,14 @@
           <t>UNIT</t>
         </is>
       </c>
+      <c r="L131" t="inlineStr"/>
       <c r="M131" t="n">
+        <v>0</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0</v>
+      </c>
+      <c r="O131" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7033,7 +7959,14 @@
           <t>UNIT</t>
         </is>
       </c>
+      <c r="L132" t="inlineStr"/>
       <c r="M132" t="n">
+        <v>0</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0</v>
+      </c>
+      <c r="O132" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7083,7 +8016,14 @@
           <t>UNIT</t>
         </is>
       </c>
+      <c r="L133" t="inlineStr"/>
       <c r="M133" t="n">
+        <v>0</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0</v>
+      </c>
+      <c r="O133" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7133,7 +8073,14 @@
           <t>UNIT</t>
         </is>
       </c>
+      <c r="L134" t="inlineStr"/>
       <c r="M134" t="n">
+        <v>0</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0</v>
+      </c>
+      <c r="O134" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7183,7 +8130,14 @@
           <t>UNIT</t>
         </is>
       </c>
+      <c r="L135" t="inlineStr"/>
       <c r="M135" t="n">
+        <v>0</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0</v>
+      </c>
+      <c r="O135" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7233,7 +8187,14 @@
           <t>UNIT</t>
         </is>
       </c>
+      <c r="L136" t="inlineStr"/>
       <c r="M136" t="n">
+        <v>0</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0</v>
+      </c>
+      <c r="O136" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7283,7 +8244,14 @@
           <t>UNIT</t>
         </is>
       </c>
+      <c r="L137" t="inlineStr"/>
       <c r="M137" t="n">
+        <v>0</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0</v>
+      </c>
+      <c r="O137" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7333,7 +8301,14 @@
           <t>UNIT</t>
         </is>
       </c>
+      <c r="L138" t="inlineStr"/>
       <c r="M138" t="n">
+        <v>0</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0</v>
+      </c>
+      <c r="O138" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7383,7 +8358,14 @@
           <t>UNIT</t>
         </is>
       </c>
+      <c r="L139" t="inlineStr"/>
       <c r="M139" t="n">
+        <v>0</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0</v>
+      </c>
+      <c r="O139" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7433,7 +8415,14 @@
           <t>UNIT</t>
         </is>
       </c>
+      <c r="L140" t="inlineStr"/>
       <c r="M140" t="n">
+        <v>0</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0</v>
+      </c>
+      <c r="O140" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7483,7 +8472,14 @@
           <t>UNIT</t>
         </is>
       </c>
+      <c r="L141" t="inlineStr"/>
       <c r="M141" t="n">
+        <v>0</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0</v>
+      </c>
+      <c r="O141" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7533,7 +8529,14 @@
           <t>UNIT</t>
         </is>
       </c>
+      <c r="L142" t="inlineStr"/>
       <c r="M142" t="n">
+        <v>0</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0</v>
+      </c>
+      <c r="O142" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7583,7 +8586,14 @@
           <t>UNIT</t>
         </is>
       </c>
+      <c r="L143" t="inlineStr"/>
       <c r="M143" t="n">
+        <v>0</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0</v>
+      </c>
+      <c r="O143" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7633,7 +8643,14 @@
           <t>UNIT</t>
         </is>
       </c>
+      <c r="L144" t="inlineStr"/>
       <c r="M144" t="n">
+        <v>0</v>
+      </c>
+      <c r="N144" t="n">
+        <v>0</v>
+      </c>
+      <c r="O144" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7725,7 +8742,6 @@
           <t>Approved</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -7759,7 +8775,6 @@
           <t>Approved</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -7793,7 +8808,6 @@
           <t>Primary</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -7827,7 +8841,6 @@
           <t>Approved</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -7861,7 +8874,6 @@
           <t>Approved</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -7895,7 +8907,6 @@
           <t>Primary</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -7929,7 +8940,6 @@
           <t>Approved</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -7963,7 +8973,6 @@
           <t>Primary</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -7997,7 +9006,6 @@
           <t>Approved</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -8031,7 +9039,6 @@
           <t>Approved</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -8065,7 +9072,6 @@
           <t>Primary</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -8099,7 +9105,6 @@
           <t>Conditional</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -8133,7 +9138,6 @@
           <t>Conditional</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -8167,7 +9171,6 @@
           <t>Approved</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -8201,7 +9204,6 @@
           <t>Sole source</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -8235,7 +9237,6 @@
           <t>Approved</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10246,7 +11247,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:J18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10280,6 +11281,26 @@
           <t>preferred</t>
         </is>
       </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>price_eur_per_unit</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>pattern_cost_eur</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>pattern_amort_qty</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -10306,23 +11327,32 @@
       <c r="F2" t="n">
         <v>1</v>
       </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MarineMetals BV</t>
+          <t>ThyssenKrupp Materials</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>NAB_CAST</t>
+          <t>SS316L</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.5</v>
+        <v>4.8</v>
       </c>
       <c r="D3" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -10331,6 +11361,15 @@
       </c>
       <c r="F3" t="n">
         <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -10341,14 +11380,14 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SS316L</t>
+          <t>SS2205</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>4.8</v>
+        <v>7.2</v>
       </c>
       <c r="D4" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -10357,6 +11396,15 @@
       </c>
       <c r="F4" t="n">
         <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -10367,14 +11415,14 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SS2205</t>
+          <t>SS174PH</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>7.2</v>
+        <v>22</v>
       </c>
       <c r="D5" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -10383,24 +11431,33 @@
       </c>
       <c r="F5" t="n">
         <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ThyssenKrupp Materials</t>
+          <t>Aalco Metals</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SS174PH</t>
+          <t>AL6082</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>22</v>
+        <v>4.8</v>
       </c>
       <c r="D6" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -10409,6 +11466,15 @@
       </c>
       <c r="F6" t="n">
         <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -10419,11 +11485,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>AL6082</t>
+          <t>AL5083</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="D7" t="n">
         <v>7</v>
@@ -10436,23 +11502,32 @@
       <c r="F7" t="n">
         <v>1</v>
       </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Aalco Metals</t>
+          <t>MarineMetals BV</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>AL5083</t>
+          <t>S355J2</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>5.1</v>
+        <v>1.35</v>
       </c>
       <c r="D8" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -10461,24 +11536,33 @@
       </c>
       <c r="F8" t="n">
         <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>MarineMetals BV</t>
+          <t>Plasticseal NL</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>S355J2</t>
+          <t>HDPE</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1.35</v>
+        <v>3.2</v>
       </c>
       <c r="D9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -10487,6 +11571,15 @@
       </c>
       <c r="F9" t="n">
         <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -10497,14 +11590,14 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>HDPE</t>
+          <t>NR_RUBBER</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3.2</v>
+        <v>8.5</v>
       </c>
       <c r="D10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -10513,24 +11606,33 @@
       </c>
       <c r="F10" t="n">
         <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Plasticseal NL</t>
+          <t>MarineMetals BV</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>NR_RUBBER</t>
+          <t>A4_FAST</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>8.5</v>
+        <v>16</v>
       </c>
       <c r="D11" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -10539,24 +11641,33 @@
       </c>
       <c r="F11" t="n">
         <v>1</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>MarineMetals BV</t>
+          <t>Titanium Industries</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>A4_FAST</t>
+          <t>TI_GR2</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="D12" t="n">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -10565,24 +11676,33 @@
       </c>
       <c r="F12" t="n">
         <v>1</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Titanium Industries</t>
+          <t>Outokumpu</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>TI_GR2</t>
+          <t>SS904L</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="D13" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -10591,24 +11711,33 @@
       </c>
       <c r="F13" t="n">
         <v>1</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Outokumpu</t>
+          <t>MarineMetals BV</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SS904L</t>
+          <t>CUNI90</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>18</v>
+        <v>14.5</v>
       </c>
       <c r="D14" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -10617,24 +11746,33 @@
       </c>
       <c r="F14" t="n">
         <v>1</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>MarineMetals BV</t>
+          <t>Goodfellow</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CUNI90</t>
+          <t>PEEK</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>14.5</v>
+        <v>88</v>
       </c>
       <c r="D15" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -10643,24 +11781,33 @@
       </c>
       <c r="F15" t="n">
         <v>1</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Goodfellow</t>
+          <t>ThyssenKrupp Materials</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>PEEK</t>
+          <t>SS316L_TUBE</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>88</v>
+        <v>7.2</v>
       </c>
       <c r="D16" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -10669,24 +11816,33 @@
       </c>
       <c r="F16" t="n">
         <v>1</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ThyssenKrupp Materials</t>
+          <t>Navalcast NL</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SS316L_TUBE</t>
+          <t>NAB_CAST</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -10694,7 +11850,61 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>15000</v>
+      </c>
+      <c r="I17" t="n">
+        <v>5</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>NAB sand castings per RFQ 2026-04. Pattern cost per pattern per part. Lead time 6 weeks from drawing release. Pressure testing included.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Wärtsilä Castings FI</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>NAB_CAST</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" t="n">
+        <v>56</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>18000</v>
+      </c>
+      <c r="I18" t="n">
+        <v>5</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Marine-grade NAB. ABS/DNV certified. Longer lead due to test certs.</t>
+        </is>
       </c>
     </row>
   </sheetData>
